--- a/TECO MOTOR.xlsx
+++ b/TECO MOTOR.xlsx
@@ -1,41 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sales 1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aerov\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1E4431-CB0A-41D8-BF3D-81AD1A700089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526F7A58-1AA0-4154-9EBF-DA047FBD1D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14595" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TECO" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="HYUNDAI" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="4" state="hidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="340">
   <si>
     <t>TECO THREE PHASE INDUCTION MOTOR PERFORMANCE DATA</t>
   </si>
@@ -1791,6 +1778,494 @@
   </si>
   <si>
     <t>TECO - EXPROOF</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>HYUNDAI - TEFC</t>
+  </si>
+  <si>
+    <t>71M</t>
+  </si>
+  <si>
+    <t>80M</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+0.5 Hp, 0.37 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1596 rpm
+Foot mounted - 71M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+0.75 Hp, 0.55 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1668 rpm
+Foot mounted - 80M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+1 Hp, 0.75 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1668 rpm
+Foot mounted - 80M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+1.5 Hp, 1.1 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1668 rpm
+Foot mounted - 90S  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+2 Hp, 1.5 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1668 rpm
+Foot mounted - 90L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+3 Hp, 2.2 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1668 rpm
+Foot mounted - 100L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+5.5 Hp, 4 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1692 rpm
+Foot mounted - 112M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+7.5 Hp, 5.5 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1722 rpm
+Foot mounted - 132S  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+10 Hp, 7.5 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1728 rpm
+Foot mounted - 132M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+10 Hp, 7.5 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+2 Pole - 3480 rpm
+Foot mounted - 132S  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+15 Hp, 11 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1728 rpm
+Foot mounted - 160M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+20 Hp, 15 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1752 rpm
+Foot mounted - 160L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+30 Hp, 22 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1764 rpm
+Foot mounted - 180L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+25 Hp, 18.5 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1752 rpm
+Foot mounted - 180M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+25 Hp, 18.5 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+6 Pole - 1176 rpm
+Foot mounted - 200L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+40 Hp, 30 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1764 rpm
+Foot mounted - 200L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+50 Hp, 37 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1764 rpm
+Foot mounted - 225S  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>250M</t>
+  </si>
+  <si>
+    <t>315L</t>
+  </si>
+  <si>
+    <t>355M</t>
+  </si>
+  <si>
+    <t>355L</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+60 Hp, 45 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1770 rpm
+Foot mounted - 225M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+75 Hp, 55 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1770 rpm
+Foot mounted - 250M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+100 Hp, 75 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1776 rpm
+Foot mounted - 280S  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+125 Hp, 90 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1776 rpm
+Foot mounted - 280M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+150 Hp, 110 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1776 rpm
+Foot mounted - 315S  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+180 Hp, 132 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1776 rpm
+Foot mounted - 315M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+200 Hp, 160 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1776 rpm
+Foot mounted - 315L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+270 Hp, 200 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1776 rpm
+Foot mounted - 315L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+340 Hp, 250 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1788 rpm
+Foot mounted - 355M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+430 Hp, 315 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1788 rpm
+Foot mounted - 355L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+475 Hp, 355 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1788 rpm
+Foot mounted - 355L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+535 Hp, 400 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1788 rpm
+Foot mounted - 355L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+0.5 Hp, 0.37 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1596 rpm
+Flange mounted - 71M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+0.75 Hp, 0.55 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1668 rpm
+Flange mounted - 80M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+1 Hp, 0.75 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1668 rpm
+Flange mounted - 80M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+1.5 Hp, 1.1 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1668 rpm
+Flange mounted - 90S  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+2 Hp, 1.5 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1668 rpm
+Flange mounted - 90L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+3 Hp, 2.2 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1668 rpm
+Flange mounted - 100L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+5.5 Hp, 4 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1692 rpm
+Flange mounted - 112M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+7.5 Hp, 5.5 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1722 rpm
+Flange mounted - 132S  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+10 Hp, 7.5 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1728 rpm
+Flange mounted - 132M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+10 Hp, 7.5 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+2 Pole - 3480 rpm
+Flange mounted - 132S  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+15 Hp, 11 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1728 rpm
+Flange mounted - 160M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+20 Hp, 15 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1752 rpm
+Flange mounted - 160L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+30 Hp, 22 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1764 rpm
+Flange mounted - 180L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+25 Hp, 18.5 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1752 rpm
+Flange mounted - 180M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+25 Hp, 18.5 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+6 Pole - 1176 rpm
+Flange mounted - 200L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+40 Hp, 30 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1764 rpm
+Flange mounted - 200L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+50 Hp, 37 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1764 rpm
+Flange mounted - 225S  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+60 Hp, 45 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1770 rpm
+Flange mounted - 225M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+75 Hp, 55 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1770 rpm
+Flange mounted - 250M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+100 Hp, 75 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1776 rpm
+Flange mounted - 280S  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+125 Hp, 90 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1776 rpm
+Flange mounted - 280M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+150 Hp, 110 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1776 rpm
+Flange mounted - 315S  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+180 Hp, 132 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1776 rpm
+Flange mounted - 315M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+200 Hp, 160 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1776 rpm
+Flange mounted - 315L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+270 Hp, 200 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1776 rpm
+Flange mounted - 315L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+340 Hp, 250 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1788 rpm
+Flange mounted - 355M  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+430 Hp, 315 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1788 rpm
+Flange mounted - 355L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+475 Hp, 355 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1788 rpm
+Flange mounted - 355L  Frame
+HYUNDAI Brand</t>
+  </si>
+  <si>
+    <t>Induction motor - TEFC
+535 Hp, 400 Kw,  3 Phase
+ 220/380/440v, 60 Hz
+4 Pole - 1788 rpm
+Flange mounted - 355L  Frame
+HYUNDAI Brand</t>
   </si>
 </sst>
 </file>
@@ -2025,32 +2500,7 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2058,9 +2508,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2112,6 +2559,34 @@
     </xf>
     <xf numFmtId="1" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2416,142 +2891,142 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W130"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
     <col min="3" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" customWidth="1"/>
+    <col min="7" max="7" width="12.86328125" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="11" width="62.5703125" customWidth="1"/>
+    <col min="9" max="11" width="62.59765625" customWidth="1"/>
     <col min="12" max="19" width="11" hidden="1" customWidth="1"/>
     <col min="20" max="23" width="14" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:23" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-    </row>
-    <row r="2" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+    </row>
+    <row r="2" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-    </row>
-    <row r="4" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+    </row>
+    <row r="4" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10" t="s">
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10" t="s">
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10" t="s">
+      <c r="S4" s="30"/>
+      <c r="T4" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10" t="s">
+      <c r="U4" s="30"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
       <c r="L5" s="1" t="s">
         <v>12</v>
       </c>
@@ -2585,22 +3060,22 @@
       <c r="V5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="W5" s="10"/>
-    </row>
-    <row r="6" spans="1:23" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="W5" s="30"/>
+    </row>
+    <row r="6" spans="1:23" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="19"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="33"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -2614,34 +3089,34 @@
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
     </row>
-    <row r="7" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="14">
         <f>A7*0.75</f>
         <v>0.75</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="15">
         <v>4</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="15">
         <v>1745</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="17">
         <v>10990</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="18">
         <f>G7*1.3</f>
         <v>14287</v>
       </c>
-      <c r="I7" s="29" t="str">
+      <c r="I7" s="19" t="str">
         <f>"Induction motor"&amp;" - "&amp;F7&amp;CHAR(10)&amp;A7&amp;" Hp, "&amp;B7&amp;" Kw, "&amp;" 3 Phase"&amp;CHAR(10)&amp;" 220/380/440v, 60 Hz"&amp;CHAR(10)&amp;C7&amp;" Pole - "&amp;D7&amp;" rpm"&amp;CHAR(10)&amp;"Foot mounted - "&amp;E7&amp;"  Frame"&amp;CHAR(10)&amp;"TECO Brand"</f>
         <v>Induction motor - Ex. Proof
 1 Hp, 0.75 Kw,  3 Phase
@@ -2650,10 +3125,12 @@
 Foot mounted - 90S  Frame
 TECO Brand</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="J7" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="K7" s="29"/>
+      <c r="K7" s="19" t="s">
+        <v>274</v>
+      </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -2685,34 +3162,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+    <row r="8" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="14">
         <f t="shared" ref="B8:B53" si="0">A8*0.75</f>
         <v>0.75</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="15">
         <v>6</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="15">
         <v>1160</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="17">
         <v>12822</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="18">
         <f t="shared" ref="H8:H14" si="1">G8*1.3</f>
         <v>16668.600000000002</v>
       </c>
-      <c r="I8" s="29" t="str">
+      <c r="I8" s="19" t="str">
         <f t="shared" ref="I8:I58" si="2">"Induction motor"&amp;" - "&amp;F8&amp;CHAR(10)&amp;A8&amp;" Hp, "&amp;B8&amp;" Kw, "&amp;" 3 Phase"&amp;CHAR(10)&amp;" 220/380/440v, 60 Hz"&amp;CHAR(10)&amp;C8&amp;" Pole - "&amp;D8&amp;" rpm"&amp;CHAR(10)&amp;"Foot mounted - "&amp;E8&amp;"  Frame"&amp;CHAR(10)&amp;"TECO Brand"</f>
         <v>Induction motor - Ex. Proof
 1 Hp, 0.75 Kw,  3 Phase
@@ -2721,10 +3198,10 @@
 Foot mounted - 90L  Frame
 TECO Brand</v>
       </c>
-      <c r="J8" s="29" t="s">
+      <c r="J8" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="K8" s="29"/>
+      <c r="K8" s="19"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -2756,33 +3233,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24">
+    <row r="9" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="14">
         <v>1.5</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="15">
         <v>2</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="15">
         <v>3480</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="17">
         <v>15617</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="18">
         <f t="shared" si="1"/>
         <v>20302.100000000002</v>
       </c>
-      <c r="I9" s="29" t="str">
+      <c r="I9" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 1.5 Hp, 1.1 Kw,  3 Phase
@@ -2791,10 +3268,10 @@
 Foot mounted - 90S  Frame
 TECO Brand</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="J9" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="K9" s="29"/>
+      <c r="K9" s="19"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -2826,33 +3303,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="24">
+    <row r="10" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="14">
         <v>1.5</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="15">
         <v>4</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="15">
         <v>1735</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="17">
         <v>19472</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="18">
         <f t="shared" si="1"/>
         <v>25313.600000000002</v>
       </c>
-      <c r="I10" s="29" t="str">
+      <c r="I10" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 1.5 Hp, 1.1 Kw,  3 Phase
@@ -2861,10 +3338,10 @@
 Foot mounted - 90L  Frame
 TECO Brand</v>
       </c>
-      <c r="J10" s="30" t="s">
+      <c r="J10" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="K10" s="29"/>
+      <c r="K10" s="19"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
@@ -2896,33 +3373,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="24">
+    <row r="11" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="14">
         <v>1.5</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="15">
         <v>6</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="15">
         <v>1150</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="17">
         <v>21015</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="18">
         <f t="shared" si="1"/>
         <v>27319.5</v>
       </c>
-      <c r="I11" s="29" t="str">
+      <c r="I11" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 1.5 Hp, 1.1 Kw,  3 Phase
@@ -2931,10 +3408,10 @@
 Foot mounted - 112S  Frame
 TECO Brand</v>
       </c>
-      <c r="J11" s="30" t="s">
+      <c r="J11" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="K11" s="29"/>
+      <c r="K11" s="19"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -2966,34 +3443,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
+    <row r="12" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="14">
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="15">
         <v>2</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="15">
         <v>3460</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="17">
         <v>24678</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="18">
         <f t="shared" si="1"/>
         <v>32081.4</v>
       </c>
-      <c r="I12" s="29" t="str">
+      <c r="I12" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 2 Hp, 1.5 Kw,  3 Phase
@@ -3002,10 +3479,10 @@
 Foot mounted - 90L  Frame
 TECO Brand</v>
       </c>
-      <c r="J12" s="29" t="s">
+      <c r="J12" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="K12" s="29"/>
+      <c r="K12" s="19"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
@@ -3037,34 +3514,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+    <row r="13" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="14">
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="15">
         <v>4</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="15">
         <v>1715</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="F13" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="17">
         <v>30656</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="18">
         <f t="shared" si="1"/>
         <v>39852.800000000003</v>
       </c>
-      <c r="I13" s="29" t="str">
+      <c r="I13" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 2 Hp, 1.5 Kw,  3 Phase
@@ -3073,10 +3550,10 @@
 Foot mounted - 90L  Frame
 TECO Brand</v>
       </c>
-      <c r="J13" s="29" t="s">
+      <c r="J13" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="K13" s="29"/>
+      <c r="K13" s="19"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -3108,34 +3585,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+    <row r="14" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="14">
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="15">
         <v>6</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="15">
         <v>1160</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="17">
         <v>34030</v>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="18">
         <f t="shared" si="1"/>
         <v>44239</v>
       </c>
-      <c r="I14" s="29" t="str">
+      <c r="I14" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 2 Hp, 1.5 Kw,  3 Phase
@@ -3144,10 +3621,10 @@
 Foot mounted - 112M  Frame
 TECO Brand</v>
       </c>
-      <c r="J14" s="29" t="s">
+      <c r="J14" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="K14" s="29"/>
+      <c r="K14" s="19"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
@@ -3179,33 +3656,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+    <row r="15" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="14">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="15">
         <v>2</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="15">
         <v>3420</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="17">
         <v>10990</v>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="18">
         <f>G15*1.3</f>
         <v>14287</v>
       </c>
-      <c r="I15" s="29" t="str">
+      <c r="I15" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 3 Hp, 2.2 Kw,  3 Phase
@@ -3214,10 +3691,10 @@
 Foot mounted - 112M  Frame
 TECO Brand</v>
       </c>
-      <c r="J15" s="30" t="s">
+      <c r="J15" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="K15" s="29"/>
+      <c r="K15" s="19"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
@@ -3249,33 +3726,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+    <row r="16" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="14">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="15">
         <v>4</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="15">
         <v>1755</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="E16" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="F16" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="17">
         <v>10990</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="18">
         <f>G16*1.3</f>
         <v>14287</v>
       </c>
-      <c r="I16" s="29" t="str">
+      <c r="I16" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 3 Hp, 2.2 Kw,  3 Phase
@@ -3284,10 +3761,10 @@
 Foot mounted - 112S  Frame
 TECO Brand</v>
       </c>
-      <c r="J16" s="30" t="s">
+      <c r="J16" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="K16" s="29"/>
+      <c r="K16" s="19"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
@@ -3319,33 +3796,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+    <row r="17" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="14">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="15">
         <v>6</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="15">
         <v>1170</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="F17" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="17">
         <v>12822</v>
       </c>
-      <c r="H17" s="28">
+      <c r="H17" s="18">
         <f t="shared" ref="H17:H23" si="3">G17*1.3</f>
         <v>16668.600000000002</v>
       </c>
-      <c r="I17" s="29" t="str">
+      <c r="I17" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 3 Hp, 2.2 Kw,  3 Phase
@@ -3354,10 +3831,10 @@
 Foot mounted - 132S  Frame
 TECO Brand</v>
       </c>
-      <c r="J17" s="29" t="s">
+      <c r="J17" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="K17" s="29"/>
+      <c r="K17" s="19"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
@@ -3389,33 +3866,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+    <row r="18" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="14">
         <v>3.75</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="15">
         <v>3450</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="E18" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="F18" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="17">
         <v>15617</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="18">
         <f t="shared" si="3"/>
         <v>20302.100000000002</v>
       </c>
-      <c r="I18" s="29" t="str">
+      <c r="I18" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 5 Hp, 3.75 Kw,  3 Phase
@@ -3424,10 +3901,10 @@
 Foot mounted - 112M  Frame
 TECO Brand</v>
       </c>
-      <c r="J18" s="29" t="s">
+      <c r="J18" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="K18" s="29"/>
+      <c r="K18" s="19"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
@@ -3459,34 +3936,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+    <row r="19" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="14">
         <f t="shared" si="0"/>
         <v>3.75</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="15">
         <v>4</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="15">
         <v>1715</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="E19" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="26" t="s">
+      <c r="F19" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="17">
         <v>19472</v>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="18">
         <f t="shared" si="3"/>
         <v>25313.600000000002</v>
       </c>
-      <c r="I19" s="29" t="str">
+      <c r="I19" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 5 Hp, 3.75 Kw,  3 Phase
@@ -3495,10 +3972,10 @@
 Foot mounted - 112M  Frame
 TECO Brand</v>
       </c>
-      <c r="J19" s="30" t="s">
+      <c r="J19" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="K19" s="29"/>
+      <c r="K19" s="19"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
@@ -3530,34 +4007,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
+    <row r="20" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="14">
         <f t="shared" si="0"/>
         <v>3.75</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="15">
         <v>6</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="15">
         <v>1160</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F20" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="17">
         <v>21015</v>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="18">
         <f t="shared" si="3"/>
         <v>27319.5</v>
       </c>
-      <c r="I20" s="29" t="str">
+      <c r="I20" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 5 Hp, 3.75 Kw,  3 Phase
@@ -3566,10 +4043,10 @@
 Foot mounted - 132M  Frame
 TECO Brand</v>
       </c>
-      <c r="J20" s="30" t="s">
+      <c r="J20" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="K20" s="29"/>
+      <c r="K20" s="19"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
@@ -3601,33 +4078,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24">
+    <row r="21" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="14">
         <v>7.5</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="14">
         <v>5.5</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="15">
         <v>2</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="15">
         <v>3470</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E21" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F21" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="17">
         <v>24678</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="18">
         <f t="shared" si="3"/>
         <v>32081.4</v>
       </c>
-      <c r="I21" s="29" t="str">
+      <c r="I21" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 7.5 Hp, 5.5 Kw,  3 Phase
@@ -3636,10 +4113,10 @@
 Foot mounted - 132S  Frame
 TECO Brand</v>
       </c>
-      <c r="J21" s="29" t="s">
+      <c r="J21" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="K21" s="29"/>
+      <c r="K21" s="19"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
@@ -3671,33 +4148,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24">
+    <row r="22" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="14">
         <v>7.5</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="14">
         <v>5.5</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="15">
         <v>4</v>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="15">
         <v>1745</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="26" t="s">
+      <c r="F22" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="17">
         <v>30656</v>
       </c>
-      <c r="H22" s="28">
+      <c r="H22" s="18">
         <f t="shared" si="3"/>
         <v>39852.800000000003</v>
       </c>
-      <c r="I22" s="29" t="str">
+      <c r="I22" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 7.5 Hp, 5.5 Kw,  3 Phase
@@ -3706,10 +4183,10 @@
 Foot mounted - 132S  Frame
 TECO Brand</v>
       </c>
-      <c r="J22" s="29" t="s">
+      <c r="J22" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="K22" s="29"/>
+      <c r="K22" s="19"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
@@ -3741,33 +4218,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24">
+    <row r="23" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="14">
         <v>7.5</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="14">
         <v>5.5</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="15">
         <v>6</v>
       </c>
-      <c r="D23" s="25">
+      <c r="D23" s="15">
         <v>1165</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F23" s="26" t="s">
+      <c r="F23" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="17">
         <v>34030</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="18">
         <f t="shared" si="3"/>
         <v>44239</v>
       </c>
-      <c r="I23" s="29" t="str">
+      <c r="I23" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 7.5 Hp, 5.5 Kw,  3 Phase
@@ -3776,10 +4253,10 @@
 Foot mounted - 160M  Frame
 TECO Brand</v>
       </c>
-      <c r="J23" s="29" t="s">
+      <c r="J23" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="K23" s="29"/>
+      <c r="K23" s="19"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
@@ -3811,34 +4288,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
+    <row r="24" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="14">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="15">
         <v>2</v>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="15">
         <v>3470</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="E24" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F24" s="26" t="s">
+      <c r="F24" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="17">
         <v>10990</v>
       </c>
-      <c r="H24" s="28">
+      <c r="H24" s="18">
         <f>G24*1.3</f>
         <v>14287</v>
       </c>
-      <c r="I24" s="29" t="str">
+      <c r="I24" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 10 Hp, 7.5 Kw,  3 Phase
@@ -3847,10 +4324,10 @@
 Foot mounted - 132M  Frame
 TECO Brand</v>
       </c>
-      <c r="J24" s="30" t="s">
+      <c r="J24" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="K24" s="29"/>
+      <c r="K24" s="19"/>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
@@ -3882,34 +4359,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="24" t="s">
+    <row r="25" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="14">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="15">
         <v>4</v>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="15">
         <v>1740</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="E25" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="17">
         <v>10990</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H25" s="18">
         <f>G25*1.3</f>
         <v>14287</v>
       </c>
-      <c r="I25" s="29" t="str">
+      <c r="I25" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 10 Hp, 7.5 Kw,  3 Phase
@@ -3918,10 +4395,10 @@
 Foot mounted - 132M  Frame
 TECO Brand</v>
       </c>
-      <c r="J25" s="30" t="s">
+      <c r="J25" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="K25" s="29"/>
+      <c r="K25" s="19"/>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
@@ -3953,34 +4430,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
+    <row r="26" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="14">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="15">
         <v>6</v>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="15">
         <v>1170</v>
       </c>
-      <c r="E26" s="27" t="s">
+      <c r="E26" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G26" s="27">
+      <c r="G26" s="17">
         <v>12822</v>
       </c>
-      <c r="H26" s="28">
+      <c r="H26" s="18">
         <f t="shared" ref="H26:H32" si="4">G26*1.3</f>
         <v>16668.600000000002</v>
       </c>
-      <c r="I26" s="29" t="str">
+      <c r="I26" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 10 Hp, 7.5 Kw,  3 Phase
@@ -3989,10 +4466,10 @@
 Foot mounted - 160L  Frame
 TECO Brand</v>
       </c>
-      <c r="J26" s="29" t="s">
+      <c r="J26" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="K26" s="29"/>
+      <c r="K26" s="19"/>
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
@@ -4024,33 +4501,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="24" t="s">
+    <row r="27" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="14">
         <v>11</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="15">
         <v>2</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="15">
         <v>3530</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="E27" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F27" s="26" t="s">
+      <c r="F27" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="17">
         <v>15617</v>
       </c>
-      <c r="H27" s="28">
+      <c r="H27" s="18">
         <f t="shared" si="4"/>
         <v>20302.100000000002</v>
       </c>
-      <c r="I27" s="29" t="str">
+      <c r="I27" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 15 Hp, 11 Kw,  3 Phase
@@ -4059,10 +4536,10 @@
 Foot mounted - 160M  Frame
 TECO Brand</v>
       </c>
-      <c r="J27" s="29" t="s">
+      <c r="J27" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="K27" s="29"/>
+      <c r="K27" s="19"/>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
@@ -4094,33 +4571,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="24" t="s">
+    <row r="28" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="14">
         <v>11</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="15">
         <v>4</v>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="15">
         <v>1760</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="E28" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F28" s="26" t="s">
+      <c r="F28" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="17">
         <v>19472</v>
       </c>
-      <c r="H28" s="28">
+      <c r="H28" s="18">
         <f t="shared" si="4"/>
         <v>25313.600000000002</v>
       </c>
-      <c r="I28" s="29" t="str">
+      <c r="I28" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 15 Hp, 11 Kw,  3 Phase
@@ -4129,10 +4606,10 @@
 Foot mounted - 160M  Frame
 TECO Brand</v>
       </c>
-      <c r="J28" s="30" t="s">
+      <c r="J28" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="K28" s="29"/>
+      <c r="K28" s="19"/>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
@@ -4164,33 +4641,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
+    <row r="29" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="14">
         <v>11</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="15">
         <v>6</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="15">
         <v>1165</v>
       </c>
-      <c r="E29" s="26" t="s">
+      <c r="E29" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="F29" s="26" t="s">
+      <c r="F29" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G29" s="27">
+      <c r="G29" s="17">
         <v>21015</v>
       </c>
-      <c r="H29" s="28">
+      <c r="H29" s="18">
         <f t="shared" si="4"/>
         <v>27319.5</v>
       </c>
-      <c r="I29" s="29" t="str">
+      <c r="I29" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 15 Hp, 11 Kw,  3 Phase
@@ -4199,10 +4676,10 @@
 Foot mounted - 180M  Frame
 TECO Brand</v>
       </c>
-      <c r="J29" s="30" t="s">
+      <c r="J29" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="K29" s="29"/>
+      <c r="K29" s="19"/>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
@@ -4234,34 +4711,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="24" t="s">
+    <row r="30" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="14">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="15">
         <v>2</v>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="15">
         <v>3520</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="E30" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="F30" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="17">
         <v>24678</v>
       </c>
-      <c r="H30" s="28">
+      <c r="H30" s="18">
         <f t="shared" si="4"/>
         <v>32081.4</v>
       </c>
-      <c r="I30" s="29" t="str">
+      <c r="I30" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 20 Hp, 15 Kw,  3 Phase
@@ -4270,10 +4747,10 @@
 Foot mounted - 160L  Frame
 TECO Brand</v>
       </c>
-      <c r="J30" s="29" t="s">
+      <c r="J30" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="K30" s="29"/>
+      <c r="K30" s="19"/>
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
@@ -4305,34 +4782,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="24" t="s">
+    <row r="31" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="14">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="15">
         <v>4</v>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="15">
         <v>1755</v>
       </c>
-      <c r="E31" s="26" t="s">
+      <c r="E31" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="F31" s="26" t="s">
+      <c r="F31" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="17">
         <v>30656</v>
       </c>
-      <c r="H31" s="28">
+      <c r="H31" s="18">
         <f t="shared" si="4"/>
         <v>39852.800000000003</v>
       </c>
-      <c r="I31" s="29" t="str">
+      <c r="I31" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 20 Hp, 15 Kw,  3 Phase
@@ -4341,10 +4818,10 @@
 Foot mounted - 160L  Frame
 TECO Brand</v>
       </c>
-      <c r="J31" s="29" t="s">
+      <c r="J31" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="K31" s="29"/>
+      <c r="K31" s="19"/>
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
@@ -4376,34 +4853,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="24" t="s">
+    <row r="32" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="14">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="15">
         <v>6</v>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="15">
         <v>1180</v>
       </c>
-      <c r="E32" s="26" t="s">
+      <c r="E32" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="F32" s="26" t="s">
+      <c r="F32" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G32" s="27">
+      <c r="G32" s="17">
         <v>34030</v>
       </c>
-      <c r="H32" s="28">
+      <c r="H32" s="18">
         <f t="shared" si="4"/>
         <v>44239</v>
       </c>
-      <c r="I32" s="29" t="str">
+      <c r="I32" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 20 Hp, 15 Kw,  3 Phase
@@ -4412,10 +4889,10 @@
 Foot mounted - 180L  Frame
 TECO Brand</v>
       </c>
-      <c r="J32" s="29" t="s">
+      <c r="J32" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="K32" s="29"/>
+      <c r="K32" s="19"/>
       <c r="L32" s="5"/>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
@@ -4447,33 +4924,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
+    <row r="33" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="B33" s="24">
+      <c r="B33" s="14">
         <v>18.5</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="15">
         <v>2</v>
       </c>
-      <c r="D33" s="25">
+      <c r="D33" s="15">
         <v>3520</v>
       </c>
-      <c r="E33" s="26" t="s">
+      <c r="E33" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="F33" s="26" t="s">
+      <c r="F33" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G33" s="27">
+      <c r="G33" s="17">
         <v>10990</v>
       </c>
-      <c r="H33" s="28">
+      <c r="H33" s="18">
         <f>G33*1.3</f>
         <v>14287</v>
       </c>
-      <c r="I33" s="29" t="str">
+      <c r="I33" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 25 Hp, 18.5 Kw,  3 Phase
@@ -4482,10 +4959,10 @@
 Foot mounted - 180MA  Frame
 TECO Brand</v>
       </c>
-      <c r="J33" s="30" t="s">
+      <c r="J33" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="K33" s="29"/>
+      <c r="K33" s="19"/>
       <c r="L33" s="5"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
@@ -4517,33 +4994,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="34" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="B34" s="24">
+      <c r="B34" s="14">
         <v>18.5</v>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="15">
         <v>4</v>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="15">
         <v>1760</v>
       </c>
-      <c r="E34" s="26" t="s">
+      <c r="E34" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="F34" s="26" t="s">
+      <c r="F34" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G34" s="27">
+      <c r="G34" s="17">
         <v>10990</v>
       </c>
-      <c r="H34" s="28">
+      <c r="H34" s="18">
         <f>G34*1.3</f>
         <v>14287</v>
       </c>
-      <c r="I34" s="29" t="str">
+      <c r="I34" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 25 Hp, 18.5 Kw,  3 Phase
@@ -4552,10 +5029,10 @@
 Foot mounted - 180M  Frame
 TECO Brand</v>
       </c>
-      <c r="J34" s="30" t="s">
+      <c r="J34" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="K34" s="29"/>
+      <c r="K34" s="19"/>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
@@ -4587,33 +5064,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="24" t="s">
+    <row r="35" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="B35" s="24">
+      <c r="B35" s="14">
         <v>18.5</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="15">
         <v>6</v>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="15">
         <v>1175</v>
       </c>
-      <c r="E35" s="27" t="s">
+      <c r="E35" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="F35" s="26" t="s">
+      <c r="F35" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G35" s="27">
+      <c r="G35" s="17">
         <v>12822</v>
       </c>
-      <c r="H35" s="28">
+      <c r="H35" s="18">
         <f t="shared" ref="H35:H41" si="5">G35*1.3</f>
         <v>16668.600000000002</v>
       </c>
-      <c r="I35" s="29" t="str">
+      <c r="I35" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 25 Hp, 18.5 Kw,  3 Phase
@@ -4622,10 +5099,10 @@
 Foot mounted - 200M  Frame
 TECO Brand</v>
       </c>
-      <c r="J35" s="29" t="s">
+      <c r="J35" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="K35" s="29"/>
+      <c r="K35" s="19"/>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
@@ -4657,33 +5134,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="36" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="B36" s="24">
+      <c r="B36" s="14">
         <v>22</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="15">
         <v>2</v>
       </c>
-      <c r="D36" s="25">
+      <c r="D36" s="15">
         <v>3530</v>
       </c>
-      <c r="E36" s="26" t="s">
+      <c r="E36" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F36" s="26" t="s">
+      <c r="F36" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G36" s="27">
+      <c r="G36" s="17">
         <v>15617</v>
       </c>
-      <c r="H36" s="28">
+      <c r="H36" s="18">
         <f t="shared" si="5"/>
         <v>20302.100000000002</v>
       </c>
-      <c r="I36" s="29" t="str">
+      <c r="I36" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 30 Hp, 22 Kw,  3 Phase
@@ -4692,10 +5169,10 @@
 Foot mounted - 180LA  Frame
 TECO Brand</v>
       </c>
-      <c r="J36" s="29" t="s">
+      <c r="J36" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="K36" s="29"/>
+      <c r="K36" s="19"/>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
@@ -4727,33 +5204,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="24" t="s">
+    <row r="37" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B37" s="14">
         <v>22</v>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="15">
         <v>4</v>
       </c>
-      <c r="D37" s="25">
+      <c r="D37" s="15">
         <v>1750</v>
       </c>
-      <c r="E37" s="26" t="s">
+      <c r="E37" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="F37" s="26" t="s">
+      <c r="F37" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G37" s="27">
+      <c r="G37" s="17">
         <v>19472</v>
       </c>
-      <c r="H37" s="28">
+      <c r="H37" s="18">
         <f t="shared" si="5"/>
         <v>25313.600000000002</v>
       </c>
-      <c r="I37" s="29" t="str">
+      <c r="I37" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 30 Hp, 22 Kw,  3 Phase
@@ -4762,10 +5239,10 @@
 Foot mounted - 180L  Frame
 TECO Brand</v>
       </c>
-      <c r="J37" s="30" t="s">
+      <c r="J37" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="K37" s="29"/>
+      <c r="K37" s="19"/>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
@@ -4797,33 +5274,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="38" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="B38" s="24">
+      <c r="B38" s="14">
         <v>22</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="15">
         <v>6</v>
       </c>
-      <c r="D38" s="25">
+      <c r="D38" s="15">
         <v>1170</v>
       </c>
-      <c r="E38" s="26" t="s">
+      <c r="E38" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="F38" s="26" t="s">
+      <c r="F38" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G38" s="27">
+      <c r="G38" s="17">
         <v>21015</v>
       </c>
-      <c r="H38" s="28">
+      <c r="H38" s="18">
         <f t="shared" si="5"/>
         <v>27319.5</v>
       </c>
-      <c r="I38" s="29" t="str">
+      <c r="I38" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 30 Hp, 22 Kw,  3 Phase
@@ -4832,10 +5309,10 @@
 Foot mounted - 200L  Frame
 TECO Brand</v>
       </c>
-      <c r="J38" s="30" t="s">
+      <c r="J38" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="K38" s="29"/>
+      <c r="K38" s="19"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
@@ -4867,34 +5344,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="24" t="s">
+    <row r="39" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="B39" s="24">
+      <c r="B39" s="14">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="15">
         <v>2</v>
       </c>
-      <c r="D39" s="25">
+      <c r="D39" s="15">
         <v>3550</v>
       </c>
-      <c r="E39" s="26" t="s">
+      <c r="E39" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="F39" s="26" t="s">
+      <c r="F39" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G39" s="27">
+      <c r="G39" s="17">
         <v>24678</v>
       </c>
-      <c r="H39" s="28">
+      <c r="H39" s="18">
         <f t="shared" si="5"/>
         <v>32081.4</v>
       </c>
-      <c r="I39" s="29" t="str">
+      <c r="I39" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 40 Hp, 30 Kw,  3 Phase
@@ -4903,10 +5380,10 @@
 Foot mounted - 200MA  Frame
 TECO Brand</v>
       </c>
-      <c r="J39" s="29" t="s">
+      <c r="J39" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="K39" s="29"/>
+      <c r="K39" s="19"/>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
@@ -4938,34 +5415,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="40" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="B40" s="24">
+      <c r="B40" s="14">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="15">
         <v>4</v>
       </c>
-      <c r="D40" s="25">
+      <c r="D40" s="15">
         <v>1760</v>
       </c>
-      <c r="E40" s="26" t="s">
+      <c r="E40" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="F40" s="26" t="s">
+      <c r="F40" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G40" s="27">
+      <c r="G40" s="17">
         <v>30656</v>
       </c>
-      <c r="H40" s="28">
+      <c r="H40" s="18">
         <f t="shared" si="5"/>
         <v>39852.800000000003</v>
       </c>
-      <c r="I40" s="29" t="str">
+      <c r="I40" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 40 Hp, 30 Kw,  3 Phase
@@ -4974,10 +5451,10 @@
 Foot mounted - 200M  Frame
 TECO Brand</v>
       </c>
-      <c r="J40" s="29" t="s">
+      <c r="J40" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="K40" s="29"/>
+      <c r="K40" s="19"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
@@ -5009,34 +5486,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="24" t="s">
+    <row r="41" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="B41" s="24">
+      <c r="B41" s="14">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="15">
         <v>6</v>
       </c>
-      <c r="D41" s="25">
+      <c r="D41" s="15">
         <v>1185</v>
       </c>
-      <c r="E41" s="26" t="s">
+      <c r="E41" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="F41" s="26" t="s">
+      <c r="F41" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G41" s="27">
+      <c r="G41" s="17">
         <v>34030</v>
       </c>
-      <c r="H41" s="28">
+      <c r="H41" s="18">
         <f t="shared" si="5"/>
         <v>44239</v>
       </c>
-      <c r="I41" s="29" t="str">
+      <c r="I41" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 40 Hp, 30 Kw,  3 Phase
@@ -5045,10 +5522,10 @@
 Foot mounted - 225S  Frame
 TECO Brand</v>
       </c>
-      <c r="J41" s="29" t="s">
+      <c r="J41" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="K41" s="29"/>
+      <c r="K41" s="19"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
@@ -5080,33 +5557,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="42" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="B42" s="24">
+      <c r="B42" s="14">
         <v>37</v>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="15">
         <v>2</v>
       </c>
-      <c r="D42" s="25">
+      <c r="D42" s="15">
         <v>3550</v>
       </c>
-      <c r="E42" s="26" t="s">
+      <c r="E42" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="F42" s="26" t="s">
+      <c r="F42" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G42" s="27">
+      <c r="G42" s="17">
         <v>10990</v>
       </c>
-      <c r="H42" s="28">
+      <c r="H42" s="18">
         <f>G42*1.3</f>
         <v>14287</v>
       </c>
-      <c r="I42" s="29" t="str">
+      <c r="I42" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 50 Hp, 37 Kw,  3 Phase
@@ -5115,10 +5592,10 @@
 Foot mounted - 200LA  Frame
 TECO Brand</v>
       </c>
-      <c r="J42" s="30" t="s">
+      <c r="J42" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="K42" s="29"/>
+      <c r="K42" s="19"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
@@ -5150,33 +5627,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="24" t="s">
+    <row r="43" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="B43" s="24">
+      <c r="B43" s="14">
         <v>37</v>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="15">
         <v>4</v>
       </c>
-      <c r="D43" s="25">
+      <c r="D43" s="15">
         <v>1760</v>
       </c>
-      <c r="E43" s="26" t="s">
+      <c r="E43" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="F43" s="26" t="s">
+      <c r="F43" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G43" s="27">
+      <c r="G43" s="17">
         <v>10990</v>
       </c>
-      <c r="H43" s="28">
+      <c r="H43" s="18">
         <f>G43*1.3</f>
         <v>14287</v>
       </c>
-      <c r="I43" s="29" t="str">
+      <c r="I43" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 50 Hp, 37 Kw,  3 Phase
@@ -5185,10 +5662,10 @@
 Foot mounted - 200L  Frame
 TECO Brand</v>
       </c>
-      <c r="J43" s="30" t="s">
+      <c r="J43" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="K43" s="29"/>
+      <c r="K43" s="19"/>
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
@@ -5220,33 +5697,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="44" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="B44" s="24">
+      <c r="B44" s="14">
         <v>37</v>
       </c>
-      <c r="C44" s="25">
+      <c r="C44" s="15">
         <v>6</v>
       </c>
-      <c r="D44" s="25">
+      <c r="D44" s="15">
         <v>1180</v>
       </c>
-      <c r="E44" s="27" t="s">
+      <c r="E44" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="F44" s="26" t="s">
+      <c r="F44" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G44" s="27">
+      <c r="G44" s="17">
         <v>12822</v>
       </c>
-      <c r="H44" s="28">
+      <c r="H44" s="18">
         <f t="shared" ref="H44:H48" si="6">G44*1.3</f>
         <v>16668.600000000002</v>
       </c>
-      <c r="I44" s="29" t="str">
+      <c r="I44" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 50 Hp, 37 Kw,  3 Phase
@@ -5255,10 +5732,10 @@
 Foot mounted - 225M  Frame
 TECO Brand</v>
       </c>
-      <c r="J44" s="29" t="s">
+      <c r="J44" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="K44" s="29"/>
+      <c r="K44" s="19"/>
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
@@ -5290,34 +5767,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="24" t="s">
+    <row r="45" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="B45" s="24">
+      <c r="B45" s="14">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C45" s="25">
+      <c r="C45" s="15">
         <v>2</v>
       </c>
-      <c r="D45" s="25">
+      <c r="D45" s="15">
         <v>3530</v>
       </c>
-      <c r="E45" s="26" t="s">
+      <c r="E45" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="F45" s="26" t="s">
+      <c r="F45" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G45" s="27">
+      <c r="G45" s="17">
         <v>19472</v>
       </c>
-      <c r="H45" s="28">
+      <c r="H45" s="18">
         <f t="shared" si="6"/>
         <v>25313.600000000002</v>
       </c>
-      <c r="I45" s="29" t="str">
+      <c r="I45" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 60 Hp, 45 Kw,  3 Phase
@@ -5326,10 +5803,10 @@
 Foot mounted - 225SA  Frame
 TECO Brand</v>
       </c>
-      <c r="J45" s="30" t="s">
+      <c r="J45" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="K45" s="29"/>
+      <c r="K45" s="19"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
@@ -5361,34 +5838,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="46" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="B46" s="24">
+      <c r="B46" s="14">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C46" s="25">
+      <c r="C46" s="15">
         <v>4</v>
       </c>
-      <c r="D46" s="25">
+      <c r="D46" s="15">
         <v>1765</v>
       </c>
-      <c r="E46" s="26" t="s">
+      <c r="E46" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="F46" s="26" t="s">
+      <c r="F46" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G46" s="27">
+      <c r="G46" s="17">
         <v>21015</v>
       </c>
-      <c r="H46" s="28">
+      <c r="H46" s="18">
         <f t="shared" si="6"/>
         <v>27319.5</v>
       </c>
-      <c r="I46" s="29" t="str">
+      <c r="I46" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 60 Hp, 45 Kw,  3 Phase
@@ -5397,10 +5874,10 @@
 Foot mounted - 225S  Frame
 TECO Brand</v>
       </c>
-      <c r="J46" s="30" t="s">
+      <c r="J46" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="K46" s="29"/>
+      <c r="K46" s="19"/>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
@@ -5432,34 +5909,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="24" t="s">
+    <row r="47" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="B47" s="24">
+      <c r="B47" s="14">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C47" s="25">
+      <c r="C47" s="15">
         <v>6</v>
       </c>
-      <c r="D47" s="25">
+      <c r="D47" s="15">
         <v>1170</v>
       </c>
-      <c r="E47" s="26" t="s">
+      <c r="E47" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="F47" s="26" t="s">
+      <c r="F47" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G47" s="27">
+      <c r="G47" s="17">
         <v>24678</v>
       </c>
-      <c r="H47" s="28">
+      <c r="H47" s="18">
         <f t="shared" si="6"/>
         <v>32081.4</v>
       </c>
-      <c r="I47" s="29" t="str">
+      <c r="I47" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 60 Hp, 45 Kw,  3 Phase
@@ -5468,10 +5945,10 @@
 Foot mounted - 250SC  Frame
 TECO Brand</v>
       </c>
-      <c r="J47" s="29" t="s">
+      <c r="J47" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="K47" s="29"/>
+      <c r="K47" s="19"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
@@ -5503,33 +5980,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="48" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="B48" s="24">
+      <c r="B48" s="14">
         <v>56</v>
       </c>
-      <c r="C48" s="25">
+      <c r="C48" s="15">
         <v>2</v>
       </c>
-      <c r="D48" s="25">
+      <c r="D48" s="15">
         <v>3540</v>
       </c>
-      <c r="E48" s="26" t="s">
+      <c r="E48" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="F48" s="26" t="s">
+      <c r="F48" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G48" s="27">
+      <c r="G48" s="17">
         <v>34030</v>
       </c>
-      <c r="H48" s="28">
+      <c r="H48" s="18">
         <f t="shared" si="6"/>
         <v>44239</v>
       </c>
-      <c r="I48" s="29" t="str">
+      <c r="I48" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 75 Hp, 56 Kw,  3 Phase
@@ -5538,10 +6015,10 @@
 Foot mounted - 225MA  Frame
 TECO Brand</v>
       </c>
-      <c r="J48" s="29" t="s">
+      <c r="J48" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="K48" s="29"/>
+      <c r="K48" s="19"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
@@ -5573,33 +6050,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="24" t="s">
+    <row r="49" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="B49" s="24">
+      <c r="B49" s="14">
         <v>56</v>
       </c>
-      <c r="C49" s="25">
+      <c r="C49" s="15">
         <v>4</v>
       </c>
-      <c r="D49" s="25">
+      <c r="D49" s="15">
         <v>1775</v>
       </c>
-      <c r="E49" s="26" t="s">
+      <c r="E49" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="F49" s="26" t="s">
+      <c r="F49" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G49" s="27">
+      <c r="G49" s="17">
         <v>10990</v>
       </c>
-      <c r="H49" s="28">
+      <c r="H49" s="18">
         <f>G49*1.3</f>
         <v>14287</v>
       </c>
-      <c r="I49" s="29" t="str">
+      <c r="I49" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 75 Hp, 56 Kw,  3 Phase
@@ -5608,10 +6085,10 @@
 Foot mounted - 225M  Frame
 TECO Brand</v>
       </c>
-      <c r="J49" s="30" t="s">
+      <c r="J49" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="K49" s="29"/>
+      <c r="K49" s="19"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
@@ -5643,33 +6120,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="24" t="s">
+    <row r="50" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="B50" s="24">
+      <c r="B50" s="14">
         <v>56</v>
       </c>
-      <c r="C50" s="25">
+      <c r="C50" s="15">
         <v>6</v>
       </c>
-      <c r="D50" s="25">
+      <c r="D50" s="15">
         <v>1175</v>
       </c>
-      <c r="E50" s="26" t="s">
+      <c r="E50" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="F50" s="26" t="s">
+      <c r="F50" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G50" s="27">
+      <c r="G50" s="17">
         <v>10990</v>
       </c>
-      <c r="H50" s="28">
+      <c r="H50" s="18">
         <f>G50*1.3</f>
         <v>14287</v>
       </c>
-      <c r="I50" s="29" t="str">
+      <c r="I50" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 75 Hp, 56 Kw,  3 Phase
@@ -5678,10 +6155,10 @@
 Foot mounted - 250MC  Frame
 TECO Brand</v>
       </c>
-      <c r="J50" s="30" t="s">
+      <c r="J50" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="K50" s="29"/>
+      <c r="K50" s="19"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
@@ -5713,34 +6190,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="24" t="s">
+    <row r="51" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="B51" s="24">
+      <c r="B51" s="14">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="C51" s="25">
+      <c r="C51" s="15">
         <v>2</v>
       </c>
-      <c r="D51" s="25">
+      <c r="D51" s="15">
         <v>3550</v>
       </c>
-      <c r="E51" s="26" t="s">
+      <c r="E51" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="F51" s="26" t="s">
+      <c r="F51" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G51" s="27">
+      <c r="G51" s="17">
         <v>15617</v>
       </c>
-      <c r="H51" s="28">
+      <c r="H51" s="18">
         <f t="shared" ref="H51:H55" si="7">G51*1.3</f>
         <v>20302.100000000002</v>
       </c>
-      <c r="I51" s="29" t="str">
+      <c r="I51" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 100 Hp, 75 Kw,  3 Phase
@@ -5749,10 +6226,10 @@
 Foot mounted - 250MA  Frame
 TECO Brand</v>
       </c>
-      <c r="J51" s="29" t="s">
+      <c r="J51" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="K51" s="29"/>
+      <c r="K51" s="19"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
@@ -5784,34 +6261,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="24" t="s">
+    <row r="52" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="B52" s="24">
+      <c r="B52" s="14">
         <f>A52*0.75</f>
         <v>75</v>
       </c>
-      <c r="C52" s="25">
+      <c r="C52" s="15">
         <v>4</v>
       </c>
-      <c r="D52" s="25">
+      <c r="D52" s="15">
         <v>1770</v>
       </c>
-      <c r="E52" s="26" t="s">
+      <c r="E52" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="F52" s="26" t="s">
+      <c r="F52" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G52" s="27">
+      <c r="G52" s="17">
         <v>19472</v>
       </c>
-      <c r="H52" s="28">
+      <c r="H52" s="18">
         <f t="shared" si="7"/>
         <v>25313.600000000002</v>
       </c>
-      <c r="I52" s="29" t="str">
+      <c r="I52" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 100 Hp, 75 Kw,  3 Phase
@@ -5820,10 +6297,10 @@
 Foot mounted - 250MC  Frame
 TECO Brand</v>
       </c>
-      <c r="J52" s="30" t="s">
+      <c r="J52" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="K52" s="29"/>
+      <c r="K52" s="19"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
@@ -5855,34 +6332,34 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="24" t="s">
+    <row r="53" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="B53" s="24">
+      <c r="B53" s="14">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="C53" s="25">
+      <c r="C53" s="15">
         <v>6</v>
       </c>
-      <c r="D53" s="25">
+      <c r="D53" s="15">
         <v>1175</v>
       </c>
-      <c r="E53" s="26" t="s">
+      <c r="E53" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="F53" s="26" t="s">
+      <c r="F53" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G53" s="27">
+      <c r="G53" s="17">
         <v>21015</v>
       </c>
-      <c r="H53" s="28">
+      <c r="H53" s="18">
         <f t="shared" si="7"/>
         <v>27319.5</v>
       </c>
-      <c r="I53" s="29" t="str">
+      <c r="I53" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 100 Hp, 75 Kw,  3 Phase
@@ -5891,10 +6368,10 @@
 Foot mounted - 280SC  Frame
 TECO Brand</v>
       </c>
-      <c r="J53" s="30" t="s">
+      <c r="J53" s="20" t="s">
         <v>259</v>
       </c>
-      <c r="K53" s="29"/>
+      <c r="K53" s="19"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
@@ -5926,33 +6403,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="24" t="s">
+    <row r="54" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="B54" s="24">
+      <c r="B54" s="14">
         <v>93</v>
       </c>
-      <c r="C54" s="25">
+      <c r="C54" s="15">
         <v>2</v>
       </c>
-      <c r="D54" s="25">
+      <c r="D54" s="15">
         <v>3555</v>
       </c>
-      <c r="E54" s="26" t="s">
+      <c r="E54" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="F54" s="26" t="s">
+      <c r="F54" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G54" s="27">
+      <c r="G54" s="17">
         <v>30656</v>
       </c>
-      <c r="H54" s="28">
+      <c r="H54" s="18">
         <f t="shared" si="7"/>
         <v>39852.800000000003</v>
       </c>
-      <c r="I54" s="29" t="str">
+      <c r="I54" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 125 Hp, 93 Kw,  3 Phase
@@ -5961,10 +6438,10 @@
 Foot mounted - 280SA  Frame
 TECO Brand</v>
       </c>
-      <c r="J54" s="29" t="s">
+      <c r="J54" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="K54" s="29"/>
+      <c r="K54" s="19"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
@@ -5996,33 +6473,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="24" t="s">
+    <row r="55" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="B55" s="24">
+      <c r="B55" s="14">
         <v>93</v>
       </c>
-      <c r="C55" s="25">
+      <c r="C55" s="15">
         <v>4</v>
       </c>
-      <c r="D55" s="25">
+      <c r="D55" s="15">
         <v>1775</v>
       </c>
-      <c r="E55" s="26" t="s">
+      <c r="E55" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="F55" s="26" t="s">
+      <c r="F55" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G55" s="27">
+      <c r="G55" s="17">
         <v>34030</v>
       </c>
-      <c r="H55" s="28">
+      <c r="H55" s="18">
         <f t="shared" si="7"/>
         <v>44239</v>
       </c>
-      <c r="I55" s="29" t="str">
+      <c r="I55" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 125 Hp, 93 Kw,  3 Phase
@@ -6031,10 +6508,10 @@
 Foot mounted - 280SC  Frame
 TECO Brand</v>
       </c>
-      <c r="J55" s="29" t="s">
+      <c r="J55" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="K55" s="29"/>
+      <c r="K55" s="19"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
@@ -6066,33 +6543,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="24" t="s">
+    <row r="56" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="B56" s="24">
+      <c r="B56" s="14">
         <v>93</v>
       </c>
-      <c r="C56" s="25">
+      <c r="C56" s="15">
         <v>6</v>
       </c>
-      <c r="D56" s="25">
+      <c r="D56" s="15">
         <v>1175</v>
       </c>
-      <c r="E56" s="26" t="s">
+      <c r="E56" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="F56" s="26" t="s">
+      <c r="F56" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G56" s="27">
+      <c r="G56" s="17">
         <v>10990</v>
       </c>
-      <c r="H56" s="28">
+      <c r="H56" s="18">
         <f>G56*1.3</f>
         <v>14287</v>
       </c>
-      <c r="I56" s="29" t="str">
+      <c r="I56" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 125 Hp, 93 Kw,  3 Phase
@@ -6101,10 +6578,10 @@
 Foot mounted - 280MC  Frame
 TECO Brand</v>
       </c>
-      <c r="J56" s="30" t="s">
+      <c r="J56" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="K56" s="29"/>
+      <c r="K56" s="19"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
@@ -6136,33 +6613,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="24" t="s">
+    <row r="57" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="B57" s="24">
+      <c r="B57" s="14">
         <v>112</v>
       </c>
-      <c r="C57" s="25">
+      <c r="C57" s="15">
         <v>2</v>
       </c>
-      <c r="D57" s="25">
+      <c r="D57" s="15">
         <v>3555</v>
       </c>
-      <c r="E57" s="26" t="s">
+      <c r="E57" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="F57" s="26" t="s">
+      <c r="F57" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G57" s="27">
+      <c r="G57" s="17">
         <v>10990</v>
       </c>
-      <c r="H57" s="28">
+      <c r="H57" s="18">
         <f>G57*1.3</f>
         <v>14287</v>
       </c>
-      <c r="I57" s="29" t="str">
+      <c r="I57" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 150 Hp, 112 Kw,  3 Phase
@@ -6171,10 +6648,10 @@
 Foot mounted - 280MA  Frame
 TECO Brand</v>
       </c>
-      <c r="J57" s="30" t="s">
+      <c r="J57" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="K57" s="29"/>
+      <c r="K57" s="19"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
@@ -6206,33 +6683,33 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="24" t="s">
+    <row r="58" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="B58" s="24">
+      <c r="B58" s="14">
         <v>112</v>
       </c>
-      <c r="C58" s="25">
+      <c r="C58" s="15">
         <v>4</v>
       </c>
-      <c r="D58" s="25">
+      <c r="D58" s="15">
         <v>1775</v>
       </c>
-      <c r="E58" s="27" t="s">
+      <c r="E58" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="F58" s="26" t="s">
+      <c r="F58" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="G58" s="27">
+      <c r="G58" s="17">
         <v>12822</v>
       </c>
-      <c r="H58" s="28">
+      <c r="H58" s="18">
         <f t="shared" ref="H58" si="8">G58*1.3</f>
         <v>16668.600000000002</v>
       </c>
-      <c r="I58" s="29" t="str">
+      <c r="I58" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Induction motor - Ex. Proof
 150 Hp, 112 Kw,  3 Phase
@@ -6241,10 +6718,10 @@
 Foot mounted - 280MC  Frame
 TECO Brand</v>
       </c>
-      <c r="J58" s="29" t="s">
+      <c r="J58" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="K58" s="29"/>
+      <c r="K58" s="19"/>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
@@ -6276,20 +6753,20 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="17" t="s">
+    <row r="59" spans="1:23" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="19"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="33"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
@@ -6303,7 +6780,7 @@
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
     </row>
-    <row r="60" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>0.25</v>
       </c>
@@ -6316,7 +6793,7 @@
       <c r="D60" s="3">
         <v>1715</v>
       </c>
-      <c r="E60" s="21" t="s">
+      <c r="E60" s="12" t="s">
         <v>176</v>
       </c>
       <c r="F60" s="4" t="s">
@@ -6325,11 +6802,11 @@
       <c r="G60" s="4">
         <v>10990</v>
       </c>
-      <c r="H60" s="23">
+      <c r="H60" s="13">
         <f>G60*1.3</f>
         <v>14287</v>
       </c>
-      <c r="I60" s="16" t="str">
+      <c r="I60" s="10" t="str">
         <f t="shared" ref="I60:I90" si="9">"Induction motor"&amp;" - "&amp;F60&amp;CHAR(10)&amp;A60&amp;" Hp, "&amp;B60&amp;" Kw, "&amp;" 3 Phase"&amp;CHAR(10)&amp;" 220/380/440v, 60 Hz"&amp;CHAR(10)&amp;C60&amp;" Pole - "&amp;D60&amp;" rpm"&amp;CHAR(10)&amp;"Foot mounted - "&amp;E60&amp;"  Frame"&amp;CHAR(10)&amp;"TECO Brand"</f>
         <v>Induction motor - TEFC
 0.25 Hp, 0.18 Kw,  3 Phase
@@ -6338,10 +6815,10 @@
 Foot mounted - A71  Frame
 TECO Brand</v>
       </c>
-      <c r="J60" s="20" t="s">
+      <c r="J60" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="K60" s="16"/>
+      <c r="K60" s="10"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
@@ -6373,7 +6850,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>0.5</v>
       </c>
@@ -6395,11 +6872,11 @@
       <c r="G61" s="4">
         <v>12822</v>
       </c>
-      <c r="H61" s="23">
+      <c r="H61" s="13">
         <f t="shared" ref="H61:H67" si="10">G61*1.3</f>
         <v>16668.600000000002</v>
       </c>
-      <c r="I61" s="16" t="str">
+      <c r="I61" s="10" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 0.5 Hp, 0.37 Kw,  3 Phase
@@ -6408,10 +6885,10 @@
 Foot mounted - 80  Frame
 TECO Brand</v>
       </c>
-      <c r="J61" s="16" t="s">
+      <c r="J61" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="K61" s="16"/>
+      <c r="K61" s="10"/>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
@@ -6443,7 +6920,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
         <v>0.75</v>
       </c>
@@ -6456,7 +6933,7 @@
       <c r="D62" s="3">
         <v>1750</v>
       </c>
-      <c r="E62" s="21" t="s">
+      <c r="E62" s="12" t="s">
         <v>177</v>
       </c>
       <c r="F62" s="4" t="s">
@@ -6465,11 +6942,11 @@
       <c r="G62" s="4">
         <v>15617</v>
       </c>
-      <c r="H62" s="23">
+      <c r="H62" s="13">
         <f t="shared" si="10"/>
         <v>20302.100000000002</v>
       </c>
-      <c r="I62" s="16" t="str">
+      <c r="I62" s="10" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 0.75 Hp, 0.55 Kw,  3 Phase
@@ -6478,10 +6955,10 @@
 Foot mounted - 90S  Frame
 TECO Brand</v>
       </c>
-      <c r="J62" s="16" t="s">
+      <c r="J62" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="K62" s="16"/>
+      <c r="K62" s="10"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
@@ -6513,7 +6990,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="2">
         <v>1</v>
       </c>
@@ -6526,7 +7003,7 @@
       <c r="D63" s="3">
         <v>1750</v>
       </c>
-      <c r="E63" s="21" t="s">
+      <c r="E63" s="12" t="s">
         <v>177</v>
       </c>
       <c r="F63" s="4" t="s">
@@ -6535,11 +7012,11 @@
       <c r="G63" s="4">
         <v>19472</v>
       </c>
-      <c r="H63" s="23">
+      <c r="H63" s="13">
         <f t="shared" si="10"/>
         <v>25313.600000000002</v>
       </c>
-      <c r="I63" s="16" t="str">
+      <c r="I63" s="10" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 1 Hp, 0.75 Kw,  3 Phase
@@ -6548,10 +7025,10 @@
 Foot mounted - 90S  Frame
 TECO Brand</v>
       </c>
-      <c r="J63" s="20" t="s">
+      <c r="J63" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="K63" s="16"/>
+      <c r="K63" s="10"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
@@ -6583,7 +7060,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="64" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
         <v>1.5</v>
       </c>
@@ -6596,7 +7073,7 @@
       <c r="D64" s="3">
         <v>1750</v>
       </c>
-      <c r="E64" s="21" t="s">
+      <c r="E64" s="12" t="s">
         <v>21</v>
       </c>
       <c r="F64" s="4" t="s">
@@ -6605,11 +7082,11 @@
       <c r="G64" s="4">
         <v>21015</v>
       </c>
-      <c r="H64" s="23">
+      <c r="H64" s="13">
         <f t="shared" si="10"/>
         <v>27319.5</v>
       </c>
-      <c r="I64" s="16" t="str">
+      <c r="I64" s="10" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 1.5 Hp, 1.1 Kw,  3 Phase
@@ -6618,10 +7095,10 @@
 Foot mounted - 90L  Frame
 TECO Brand</v>
       </c>
-      <c r="J64" s="20" t="s">
+      <c r="J64" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="K64" s="16"/>
+      <c r="K64" s="10"/>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
@@ -6653,7 +7130,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="65" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
         <v>2</v>
       </c>
@@ -6666,7 +7143,7 @@
       <c r="D65" s="3">
         <v>1760</v>
       </c>
-      <c r="E65" s="21" t="s">
+      <c r="E65" s="12" t="s">
         <v>22</v>
       </c>
       <c r="F65" s="4" t="s">
@@ -6675,11 +7152,11 @@
       <c r="G65" s="4">
         <v>24678</v>
       </c>
-      <c r="H65" s="23">
+      <c r="H65" s="13">
         <f t="shared" si="10"/>
         <v>32081.4</v>
       </c>
-      <c r="I65" s="16" t="str">
+      <c r="I65" s="10" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 2 Hp, 1.5 Kw,  3 Phase
@@ -6688,10 +7165,10 @@
 Foot mounted - 100L  Frame
 TECO Brand</v>
       </c>
-      <c r="J65" s="16" t="s">
+      <c r="J65" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="K65" s="16"/>
+      <c r="K65" s="10"/>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
@@ -6723,7 +7200,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>3</v>
       </c>
@@ -6736,7 +7213,7 @@
       <c r="D66" s="3">
         <v>1760</v>
       </c>
-      <c r="E66" s="21" t="s">
+      <c r="E66" s="12" t="s">
         <v>178</v>
       </c>
       <c r="F66" s="4" t="s">
@@ -6745,11 +7222,11 @@
       <c r="G66" s="4">
         <v>30656</v>
       </c>
-      <c r="H66" s="23">
+      <c r="H66" s="13">
         <f t="shared" si="10"/>
         <v>39852.800000000003</v>
       </c>
-      <c r="I66" s="16" t="str">
+      <c r="I66" s="10" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 3 Hp, 2.2 Kw,  3 Phase
@@ -6758,10 +7235,10 @@
 Foot mounted - 112S  Frame
 TECO Brand</v>
       </c>
-      <c r="J66" s="16" t="s">
+      <c r="J66" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="K66" s="16"/>
+      <c r="K66" s="10"/>
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
@@ -6793,7 +7270,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
         <v>5</v>
       </c>
@@ -6806,7 +7283,7 @@
       <c r="D67" s="3">
         <v>1750</v>
       </c>
-      <c r="E67" s="21" t="s">
+      <c r="E67" s="12" t="s">
         <v>23</v>
       </c>
       <c r="F67" s="4" t="s">
@@ -6815,11 +7292,11 @@
       <c r="G67" s="4">
         <v>34030</v>
       </c>
-      <c r="H67" s="23">
+      <c r="H67" s="13">
         <f t="shared" si="10"/>
         <v>44239</v>
       </c>
-      <c r="I67" s="16" t="str">
+      <c r="I67" s="10" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 5 Hp, 3.7 Kw,  3 Phase
@@ -6828,10 +7305,10 @@
 Foot mounted - 112M  Frame
 TECO Brand</v>
       </c>
-      <c r="J67" s="16" t="s">
+      <c r="J67" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="K67" s="16"/>
+      <c r="K67" s="10"/>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
@@ -6863,20 +7340,20 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:23" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="17" t="s">
+    <row r="68" spans="1:23" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="18"/>
-      <c r="E68" s="18"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="18"/>
-      <c r="H68" s="18"/>
-      <c r="I68" s="18"/>
-      <c r="J68" s="18"/>
-      <c r="K68" s="19"/>
+      <c r="B68" s="32"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="32"/>
+      <c r="J68" s="32"/>
+      <c r="K68" s="33"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
       <c r="N68" s="1"/>
@@ -6890,28 +7367,28 @@
       <c r="V68" s="1"/>
       <c r="W68" s="1"/>
     </row>
-    <row r="69" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="35">
+    <row r="69" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A69" s="25">
         <v>0.5</v>
       </c>
-      <c r="B69" s="35">
+      <c r="B69" s="25">
         <v>0.37</v>
       </c>
-      <c r="C69" s="36">
+      <c r="C69" s="26">
         <v>2</v>
       </c>
-      <c r="D69" s="36">
+      <c r="D69" s="26">
         <v>3400</v>
       </c>
-      <c r="E69" s="37" t="s">
+      <c r="E69" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="F69" s="33" t="s">
+      <c r="F69" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G69" s="33"/>
-      <c r="H69" s="33"/>
-      <c r="I69" s="34" t="str">
+      <c r="G69" s="23"/>
+      <c r="H69" s="23"/>
+      <c r="I69" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 0.5 Hp, 0.37 Kw,  3 Phase
@@ -6920,10 +7397,10 @@
 Foot mounted - 71  Frame
 TECO Brand</v>
       </c>
-      <c r="J69" s="34" t="s">
+      <c r="J69" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="K69" s="34" t="s">
+      <c r="K69" s="24" t="s">
         <v>49</v>
       </c>
       <c r="L69" s="8">
@@ -6963,28 +7440,28 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="31">
+    <row r="70" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A70" s="21">
         <v>0.5</v>
       </c>
-      <c r="B70" s="31">
+      <c r="B70" s="21">
         <v>0.37</v>
       </c>
-      <c r="C70" s="32">
+      <c r="C70" s="22">
         <v>4</v>
       </c>
-      <c r="D70" s="32">
+      <c r="D70" s="22">
         <v>1680</v>
       </c>
-      <c r="E70" s="33" t="s">
+      <c r="E70" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="F70" s="33" t="s">
+      <c r="F70" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G70" s="33"/>
-      <c r="H70" s="33"/>
-      <c r="I70" s="34" t="str">
+      <c r="G70" s="23"/>
+      <c r="H70" s="23"/>
+      <c r="I70" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 0.5 Hp, 0.37 Kw,  3 Phase
@@ -6993,10 +7470,10 @@
 Foot mounted - 71  Frame
 TECO Brand</v>
       </c>
-      <c r="J70" s="34" t="s">
+      <c r="J70" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="K70" s="34" t="s">
+      <c r="K70" s="24" t="s">
         <v>50</v>
       </c>
       <c r="L70" s="5">
@@ -7036,28 +7513,28 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="71" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="35">
+    <row r="71" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="25">
         <v>0.5</v>
       </c>
-      <c r="B71" s="35">
+      <c r="B71" s="25">
         <v>0.37</v>
       </c>
-      <c r="C71" s="36">
+      <c r="C71" s="26">
         <v>6</v>
       </c>
-      <c r="D71" s="36">
+      <c r="D71" s="26">
         <v>1135</v>
       </c>
-      <c r="E71" s="37" t="s">
+      <c r="E71" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F71" s="33" t="s">
+      <c r="F71" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G71" s="33"/>
-      <c r="H71" s="33"/>
-      <c r="I71" s="34" t="str">
+      <c r="G71" s="23"/>
+      <c r="H71" s="23"/>
+      <c r="I71" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 0.5 Hp, 0.37 Kw,  3 Phase
@@ -7066,10 +7543,10 @@
 Foot mounted - 80  Frame
 TECO Brand</v>
       </c>
-      <c r="J71" s="34" t="s">
+      <c r="J71" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="K71" s="34" t="s">
+      <c r="K71" s="24" t="s">
         <v>51</v>
       </c>
       <c r="L71" s="8">
@@ -7109,28 +7586,28 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="38">
+    <row r="72" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A72" s="28">
         <v>1</v>
       </c>
-      <c r="B72" s="31">
+      <c r="B72" s="21">
         <v>0.75</v>
       </c>
-      <c r="C72" s="32">
+      <c r="C72" s="22">
         <v>2</v>
       </c>
-      <c r="D72" s="32">
+      <c r="D72" s="22">
         <v>3395</v>
       </c>
-      <c r="E72" s="33" t="s">
+      <c r="E72" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="F72" s="33" t="s">
+      <c r="F72" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G72" s="33"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="34" t="str">
+      <c r="G72" s="23"/>
+      <c r="H72" s="23"/>
+      <c r="I72" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 1 Hp, 0.75 Kw,  3 Phase
@@ -7139,10 +7616,10 @@
 Foot mounted - 80  Frame
 TECO Brand</v>
       </c>
-      <c r="J72" s="34" t="s">
+      <c r="J72" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="K72" s="34" t="s">
+      <c r="K72" s="24" t="s">
         <v>52</v>
       </c>
       <c r="L72" s="5">
@@ -7182,28 +7659,28 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="39">
+    <row r="73" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A73" s="29">
         <v>1</v>
       </c>
-      <c r="B73" s="35">
+      <c r="B73" s="25">
         <v>0.75</v>
       </c>
-      <c r="C73" s="36">
+      <c r="C73" s="26">
         <v>4</v>
       </c>
-      <c r="D73" s="36">
+      <c r="D73" s="26">
         <v>1710</v>
       </c>
-      <c r="E73" s="37" t="s">
+      <c r="E73" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F73" s="33" t="s">
+      <c r="F73" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G73" s="33"/>
-      <c r="H73" s="33"/>
-      <c r="I73" s="34" t="str">
+      <c r="G73" s="23"/>
+      <c r="H73" s="23"/>
+      <c r="I73" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 1 Hp, 0.75 Kw,  3 Phase
@@ -7212,10 +7689,10 @@
 Foot mounted - 80  Frame
 TECO Brand</v>
       </c>
-      <c r="J73" s="34" t="s">
+      <c r="J73" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="K73" s="34" t="s">
+      <c r="K73" s="24" t="s">
         <v>53</v>
       </c>
       <c r="L73" s="8">
@@ -7255,28 +7732,28 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="38">
+    <row r="74" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A74" s="28">
         <v>1</v>
       </c>
-      <c r="B74" s="31">
+      <c r="B74" s="21">
         <v>0.75</v>
       </c>
-      <c r="C74" s="32">
+      <c r="C74" s="22">
         <v>6</v>
       </c>
-      <c r="D74" s="32">
+      <c r="D74" s="22">
         <v>1140</v>
       </c>
-      <c r="E74" s="33" t="s">
+      <c r="E74" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="F74" s="33" t="s">
+      <c r="F74" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G74" s="33"/>
-      <c r="H74" s="33"/>
-      <c r="I74" s="34" t="str">
+      <c r="G74" s="23"/>
+      <c r="H74" s="23"/>
+      <c r="I74" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 1 Hp, 0.75 Kw,  3 Phase
@@ -7285,10 +7762,10 @@
 Foot mounted - 90L  Frame
 TECO Brand</v>
       </c>
-      <c r="J74" s="34" t="s">
+      <c r="J74" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="K74" s="34" t="s">
+      <c r="K74" s="24" t="s">
         <v>54</v>
       </c>
       <c r="L74" s="5">
@@ -7328,28 +7805,28 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="39">
+    <row r="75" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="29">
         <v>2</v>
       </c>
-      <c r="B75" s="35">
+      <c r="B75" s="25">
         <v>1.5</v>
       </c>
-      <c r="C75" s="36">
+      <c r="C75" s="26">
         <v>2</v>
       </c>
-      <c r="D75" s="36">
+      <c r="D75" s="26">
         <v>3425</v>
       </c>
-      <c r="E75" s="37" t="s">
+      <c r="E75" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="F75" s="33" t="s">
+      <c r="F75" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G75" s="33"/>
-      <c r="H75" s="33"/>
-      <c r="I75" s="34" t="str">
+      <c r="G75" s="23"/>
+      <c r="H75" s="23"/>
+      <c r="I75" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 2 Hp, 1.5 Kw,  3 Phase
@@ -7358,10 +7835,10 @@
 Foot mounted - 90L  Frame
 TECO Brand</v>
       </c>
-      <c r="J75" s="34" t="s">
+      <c r="J75" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="K75" s="34" t="s">
+      <c r="K75" s="24" t="s">
         <v>55</v>
       </c>
       <c r="L75" s="8">
@@ -7401,28 +7878,28 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="76" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="38">
+    <row r="76" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="28">
         <v>2</v>
       </c>
-      <c r="B76" s="31">
+      <c r="B76" s="21">
         <v>1.5</v>
       </c>
-      <c r="C76" s="32">
+      <c r="C76" s="22">
         <v>4</v>
       </c>
-      <c r="D76" s="32">
+      <c r="D76" s="22">
         <v>1715</v>
       </c>
-      <c r="E76" s="33" t="s">
+      <c r="E76" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="F76" s="33" t="s">
+      <c r="F76" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G76" s="33"/>
-      <c r="H76" s="33"/>
-      <c r="I76" s="34" t="str">
+      <c r="G76" s="23"/>
+      <c r="H76" s="23"/>
+      <c r="I76" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 2 Hp, 1.5 Kw,  3 Phase
@@ -7431,10 +7908,10 @@
 Foot mounted - 90L  Frame
 TECO Brand</v>
       </c>
-      <c r="J76" s="34" t="s">
+      <c r="J76" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="K76" s="34" t="s">
+      <c r="K76" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L76" s="5">
@@ -7474,28 +7951,28 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="39">
+    <row r="77" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A77" s="29">
         <v>2</v>
       </c>
-      <c r="B77" s="35">
+      <c r="B77" s="25">
         <v>1.5</v>
       </c>
-      <c r="C77" s="36">
+      <c r="C77" s="26">
         <v>6</v>
       </c>
-      <c r="D77" s="36">
+      <c r="D77" s="26">
         <v>1140</v>
       </c>
-      <c r="E77" s="37" t="s">
+      <c r="E77" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F77" s="33" t="s">
+      <c r="F77" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G77" s="33"/>
-      <c r="H77" s="33"/>
-      <c r="I77" s="34" t="str">
+      <c r="G77" s="23"/>
+      <c r="H77" s="23"/>
+      <c r="I77" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 2 Hp, 1.5 Kw,  3 Phase
@@ -7504,10 +7981,10 @@
 Foot mounted - 100L  Frame
 TECO Brand</v>
       </c>
-      <c r="J77" s="34" t="s">
+      <c r="J77" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="K77" s="34" t="s">
+      <c r="K77" s="24" t="s">
         <v>57</v>
       </c>
       <c r="L77" s="8">
@@ -7547,28 +8024,28 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="38">
+    <row r="78" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="28">
         <v>3</v>
       </c>
-      <c r="B78" s="31">
+      <c r="B78" s="21">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C78" s="32">
+      <c r="C78" s="22">
         <v>2</v>
       </c>
-      <c r="D78" s="32">
+      <c r="D78" s="22">
         <v>3450</v>
       </c>
-      <c r="E78" s="33" t="s">
+      <c r="E78" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="F78" s="33" t="s">
+      <c r="F78" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G78" s="33"/>
-      <c r="H78" s="33"/>
-      <c r="I78" s="34" t="str">
+      <c r="G78" s="23"/>
+      <c r="H78" s="23"/>
+      <c r="I78" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 3 Hp, 2.2 Kw,  3 Phase
@@ -7577,10 +8054,10 @@
 Foot mounted - 90L  Frame
 TECO Brand</v>
       </c>
-      <c r="J78" s="34" t="s">
+      <c r="J78" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="K78" s="34" t="s">
+      <c r="K78" s="24" t="s">
         <v>58</v>
       </c>
       <c r="L78" s="5">
@@ -7620,28 +8097,28 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="39">
+    <row r="79" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A79" s="29">
         <v>3</v>
       </c>
-      <c r="B79" s="35">
+      <c r="B79" s="25">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C79" s="36">
+      <c r="C79" s="26">
         <v>4</v>
       </c>
-      <c r="D79" s="36">
+      <c r="D79" s="26">
         <v>1735</v>
       </c>
-      <c r="E79" s="37" t="s">
+      <c r="E79" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F79" s="33" t="s">
+      <c r="F79" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G79" s="33"/>
-      <c r="H79" s="33"/>
-      <c r="I79" s="34" t="str">
+      <c r="G79" s="23"/>
+      <c r="H79" s="23"/>
+      <c r="I79" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 3 Hp, 2.2 Kw,  3 Phase
@@ -7650,10 +8127,10 @@
 Foot mounted - 100L  Frame
 TECO Brand</v>
       </c>
-      <c r="J79" s="34" t="s">
+      <c r="J79" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="K79" s="34" t="s">
+      <c r="K79" s="24" t="s">
         <v>59</v>
       </c>
       <c r="L79" s="8">
@@ -7693,28 +8170,28 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="38">
+    <row r="80" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A80" s="28">
         <v>3</v>
       </c>
-      <c r="B80" s="31">
+      <c r="B80" s="21">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C80" s="32">
+      <c r="C80" s="22">
         <v>6</v>
       </c>
-      <c r="D80" s="32">
+      <c r="D80" s="22">
         <v>1160</v>
       </c>
-      <c r="E80" s="33" t="s">
+      <c r="E80" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="F80" s="33" t="s">
+      <c r="F80" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G80" s="33"/>
-      <c r="H80" s="33"/>
-      <c r="I80" s="34" t="str">
+      <c r="G80" s="23"/>
+      <c r="H80" s="23"/>
+      <c r="I80" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 3 Hp, 2.2 Kw,  3 Phase
@@ -7723,10 +8200,10 @@
 Foot mounted - 112M  Frame
 TECO Brand</v>
       </c>
-      <c r="J80" s="34" t="s">
+      <c r="J80" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="K80" s="34" t="s">
+      <c r="K80" s="24" t="s">
         <v>60</v>
       </c>
       <c r="L80" s="5">
@@ -7766,28 +8243,28 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="39">
+    <row r="81" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A81" s="29">
         <v>5</v>
       </c>
-      <c r="B81" s="35">
+      <c r="B81" s="25">
         <v>3.7</v>
       </c>
-      <c r="C81" s="36">
+      <c r="C81" s="26">
         <v>2</v>
       </c>
-      <c r="D81" s="36">
+      <c r="D81" s="26">
         <v>3485</v>
       </c>
-      <c r="E81" s="37" t="s">
+      <c r="E81" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="F81" s="33" t="s">
+      <c r="F81" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G81" s="33"/>
-      <c r="H81" s="33"/>
-      <c r="I81" s="34" t="str">
+      <c r="G81" s="23"/>
+      <c r="H81" s="23"/>
+      <c r="I81" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 5 Hp, 3.7 Kw,  3 Phase
@@ -7796,10 +8273,10 @@
 Foot mounted - 112M  Frame
 TECO Brand</v>
       </c>
-      <c r="J81" s="34" t="s">
+      <c r="J81" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="K81" s="34" t="s">
+      <c r="K81" s="24" t="s">
         <v>61</v>
       </c>
       <c r="L81" s="8">
@@ -7839,28 +8316,28 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="38">
+    <row r="82" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A82" s="28">
         <v>5</v>
       </c>
-      <c r="B82" s="31">
+      <c r="B82" s="21">
         <v>3.7</v>
       </c>
-      <c r="C82" s="32">
+      <c r="C82" s="22">
         <v>4</v>
       </c>
-      <c r="D82" s="32">
+      <c r="D82" s="22">
         <v>1745</v>
       </c>
-      <c r="E82" s="33" t="s">
+      <c r="E82" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="F82" s="33" t="s">
+      <c r="F82" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G82" s="33"/>
-      <c r="H82" s="33"/>
-      <c r="I82" s="34" t="str">
+      <c r="G82" s="23"/>
+      <c r="H82" s="23"/>
+      <c r="I82" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 5 Hp, 3.7 Kw,  3 Phase
@@ -7869,10 +8346,10 @@
 Foot mounted - 112M  Frame
 TECO Brand</v>
       </c>
-      <c r="J82" s="34" t="s">
+      <c r="J82" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="K82" s="34" t="s">
+      <c r="K82" s="24" t="s">
         <v>62</v>
       </c>
       <c r="L82" s="5">
@@ -7912,28 +8389,28 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="39">
+    <row r="83" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A83" s="29">
         <v>5</v>
       </c>
-      <c r="B83" s="35">
+      <c r="B83" s="25">
         <v>3.7</v>
       </c>
-      <c r="C83" s="36">
+      <c r="C83" s="26">
         <v>6</v>
       </c>
-      <c r="D83" s="36">
+      <c r="D83" s="26">
         <v>1160</v>
       </c>
-      <c r="E83" s="37" t="s">
+      <c r="E83" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="F83" s="33" t="s">
+      <c r="F83" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G83" s="33"/>
-      <c r="H83" s="33"/>
-      <c r="I83" s="34" t="str">
+      <c r="G83" s="23"/>
+      <c r="H83" s="23"/>
+      <c r="I83" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 5 Hp, 3.7 Kw,  3 Phase
@@ -7942,10 +8419,10 @@
 Foot mounted - 132S  Frame
 TECO Brand</v>
       </c>
-      <c r="J83" s="34" t="s">
+      <c r="J83" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="K83" s="34" t="s">
+      <c r="K83" s="24" t="s">
         <v>63</v>
       </c>
       <c r="L83" s="8">
@@ -7985,28 +8462,28 @@
         <v>0.151</v>
       </c>
     </row>
-    <row r="84" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="31">
+    <row r="84" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A84" s="21">
         <v>7.5</v>
       </c>
-      <c r="B84" s="31">
+      <c r="B84" s="21">
         <v>5.5</v>
       </c>
-      <c r="C84" s="32">
+      <c r="C84" s="22">
         <v>2</v>
       </c>
-      <c r="D84" s="32">
+      <c r="D84" s="22">
         <v>3505</v>
       </c>
-      <c r="E84" s="33" t="s">
+      <c r="E84" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F84" s="33" t="s">
+      <c r="F84" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G84" s="33"/>
-      <c r="H84" s="33"/>
-      <c r="I84" s="34" t="str">
+      <c r="G84" s="23"/>
+      <c r="H84" s="23"/>
+      <c r="I84" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 7.5 Hp, 5.5 Kw,  3 Phase
@@ -8015,10 +8492,10 @@
 Foot mounted - 132S  Frame
 TECO Brand</v>
       </c>
-      <c r="J84" s="34" t="s">
+      <c r="J84" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="K84" s="34" t="s">
+      <c r="K84" s="24" t="s">
         <v>64</v>
       </c>
       <c r="L84" s="5">
@@ -8058,28 +8535,28 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="35">
+    <row r="85" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A85" s="25">
         <v>7.5</v>
       </c>
-      <c r="B85" s="35">
+      <c r="B85" s="25">
         <v>5.5</v>
       </c>
-      <c r="C85" s="36">
+      <c r="C85" s="26">
         <v>4</v>
       </c>
-      <c r="D85" s="36">
+      <c r="D85" s="26">
         <v>1750</v>
       </c>
-      <c r="E85" s="37" t="s">
+      <c r="E85" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="F85" s="33" t="s">
+      <c r="F85" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G85" s="33"/>
-      <c r="H85" s="33"/>
-      <c r="I85" s="34" t="str">
+      <c r="G85" s="23"/>
+      <c r="H85" s="23"/>
+      <c r="I85" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 7.5 Hp, 5.5 Kw,  3 Phase
@@ -8088,10 +8565,10 @@
 Foot mounted - 132S  Frame
 TECO Brand</v>
       </c>
-      <c r="J85" s="34" t="s">
+      <c r="J85" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="K85" s="34" t="s">
+      <c r="K85" s="24" t="s">
         <v>65</v>
       </c>
       <c r="L85" s="8">
@@ -8131,28 +8608,28 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="86" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="31">
+    <row r="86" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A86" s="21">
         <v>7.5</v>
       </c>
-      <c r="B86" s="31">
+      <c r="B86" s="21">
         <v>5.5</v>
       </c>
-      <c r="C86" s="32">
+      <c r="C86" s="22">
         <v>6</v>
       </c>
-      <c r="D86" s="32">
+      <c r="D86" s="22">
         <v>1160</v>
       </c>
-      <c r="E86" s="33" t="s">
+      <c r="E86" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F86" s="33" t="s">
+      <c r="F86" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G86" s="33"/>
-      <c r="H86" s="33"/>
-      <c r="I86" s="34" t="str">
+      <c r="G86" s="23"/>
+      <c r="H86" s="23"/>
+      <c r="I86" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 7.5 Hp, 5.5 Kw,  3 Phase
@@ -8161,10 +8638,10 @@
 Foot mounted - 132M  Frame
 TECO Brand</v>
       </c>
-      <c r="J86" s="34" t="s">
+      <c r="J86" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="K86" s="34" t="s">
+      <c r="K86" s="24" t="s">
         <v>66</v>
       </c>
       <c r="L86" s="5">
@@ -8204,28 +8681,28 @@
         <v>0.217</v>
       </c>
     </row>
-    <row r="87" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="39">
+    <row r="87" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A87" s="29">
         <v>10</v>
       </c>
-      <c r="B87" s="35">
+      <c r="B87" s="25">
         <v>7.5</v>
       </c>
-      <c r="C87" s="36">
+      <c r="C87" s="26">
         <v>2</v>
       </c>
-      <c r="D87" s="36">
+      <c r="D87" s="26">
         <v>3510</v>
       </c>
-      <c r="E87" s="37" t="s">
+      <c r="E87" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="F87" s="33" t="s">
+      <c r="F87" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G87" s="33"/>
-      <c r="H87" s="33"/>
-      <c r="I87" s="34" t="str">
+      <c r="G87" s="23"/>
+      <c r="H87" s="23"/>
+      <c r="I87" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 10 Hp, 7.5 Kw,  3 Phase
@@ -8234,10 +8711,10 @@
 Foot mounted - 132S  Frame
 TECO Brand</v>
       </c>
-      <c r="J87" s="34" t="s">
+      <c r="J87" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="K87" s="34" t="s">
+      <c r="K87" s="24" t="s">
         <v>67</v>
       </c>
       <c r="L87" s="8">
@@ -8277,28 +8754,28 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="38">
+    <row r="88" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A88" s="28">
         <v>10</v>
       </c>
-      <c r="B88" s="31">
+      <c r="B88" s="21">
         <v>7.5</v>
       </c>
-      <c r="C88" s="32">
+      <c r="C88" s="22">
         <v>4</v>
       </c>
-      <c r="D88" s="32">
+      <c r="D88" s="22">
         <v>1750</v>
       </c>
-      <c r="E88" s="33" t="s">
+      <c r="E88" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F88" s="33" t="s">
+      <c r="F88" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G88" s="33"/>
-      <c r="H88" s="33"/>
-      <c r="I88" s="34" t="str">
+      <c r="G88" s="23"/>
+      <c r="H88" s="23"/>
+      <c r="I88" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 10 Hp, 7.5 Kw,  3 Phase
@@ -8307,10 +8784,10 @@
 Foot mounted - 132M  Frame
 TECO Brand</v>
       </c>
-      <c r="J88" s="34" t="s">
+      <c r="J88" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="K88" s="34" t="s">
+      <c r="K88" s="24" t="s">
         <v>68</v>
       </c>
       <c r="L88" s="5">
@@ -8350,28 +8827,28 @@
         <v>0.14299999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="39">
+    <row r="89" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="29">
         <v>10</v>
       </c>
-      <c r="B89" s="35">
+      <c r="B89" s="25">
         <v>7.5</v>
       </c>
-      <c r="C89" s="36">
+      <c r="C89" s="26">
         <v>6</v>
       </c>
-      <c r="D89" s="36">
+      <c r="D89" s="26">
         <v>1175</v>
       </c>
-      <c r="E89" s="37" t="s">
+      <c r="E89" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="F89" s="33" t="s">
+      <c r="F89" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G89" s="33"/>
-      <c r="H89" s="33"/>
-      <c r="I89" s="34" t="str">
+      <c r="G89" s="23"/>
+      <c r="H89" s="23"/>
+      <c r="I89" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 10 Hp, 7.5 Kw,  3 Phase
@@ -8380,10 +8857,10 @@
 Foot mounted - 160M  Frame
 TECO Brand</v>
       </c>
-      <c r="J89" s="34" t="s">
+      <c r="J89" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="K89" s="34" t="s">
+      <c r="K89" s="24" t="s">
         <v>69</v>
       </c>
       <c r="L89" s="8">
@@ -8423,28 +8900,28 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="90" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="38">
+    <row r="90" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A90" s="28">
         <v>15</v>
       </c>
-      <c r="B90" s="38">
+      <c r="B90" s="28">
         <v>11</v>
       </c>
-      <c r="C90" s="32">
+      <c r="C90" s="22">
         <v>2</v>
       </c>
-      <c r="D90" s="32">
+      <c r="D90" s="22">
         <v>3540</v>
       </c>
-      <c r="E90" s="33" t="s">
+      <c r="E90" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="F90" s="33" t="s">
+      <c r="F90" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G90" s="33"/>
-      <c r="H90" s="33"/>
-      <c r="I90" s="34" t="str">
+      <c r="G90" s="23"/>
+      <c r="H90" s="23"/>
+      <c r="I90" s="24" t="str">
         <f t="shared" si="9"/>
         <v>Induction motor - TEFC
 15 Hp, 11 Kw,  3 Phase
@@ -8453,10 +8930,10 @@
 Foot mounted - 160M  Frame
 TECO Brand</v>
       </c>
-      <c r="J90" s="34" t="s">
+      <c r="J90" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="K90" s="34" t="s">
+      <c r="K90" s="24" t="s">
         <v>70</v>
       </c>
       <c r="L90" s="5">
@@ -8496,28 +8973,28 @@
         <v>0.14699999999999999</v>
       </c>
     </row>
-    <row r="91" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="39">
+    <row r="91" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A91" s="29">
         <v>15</v>
       </c>
-      <c r="B91" s="39">
+      <c r="B91" s="29">
         <v>11</v>
       </c>
-      <c r="C91" s="36">
+      <c r="C91" s="26">
         <v>4</v>
       </c>
-      <c r="D91" s="36">
+      <c r="D91" s="26">
         <v>1760</v>
       </c>
-      <c r="E91" s="37" t="s">
+      <c r="E91" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="F91" s="33" t="s">
+      <c r="F91" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G91" s="33"/>
-      <c r="H91" s="33"/>
-      <c r="I91" s="34" t="str">
+      <c r="G91" s="23"/>
+      <c r="H91" s="23"/>
+      <c r="I91" s="24" t="str">
         <f t="shared" ref="I91:I130" si="11">"Induction motor"&amp;" - "&amp;F91&amp;CHAR(10)&amp;A91&amp;" Hp, "&amp;B91&amp;" Kw, "&amp;" 3 Phase"&amp;CHAR(10)&amp;" 220/380/440v, 60 Hz"&amp;CHAR(10)&amp;C91&amp;" Pole - "&amp;D91&amp;" rpm"&amp;CHAR(10)&amp;"Foot mounted - "&amp;E91&amp;"  Frame"&amp;CHAR(10)&amp;"TECO Brand"</f>
         <v>Induction motor - TEFC
 15 Hp, 11 Kw,  3 Phase
@@ -8526,10 +9003,10 @@
 Foot mounted - 160M  Frame
 TECO Brand</v>
       </c>
-      <c r="J91" s="34" t="s">
+      <c r="J91" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="K91" s="34" t="s">
+      <c r="K91" s="24" t="s">
         <v>71</v>
       </c>
       <c r="L91" s="8">
@@ -8569,28 +9046,28 @@
         <v>0.29699999999999999</v>
       </c>
     </row>
-    <row r="92" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="38">
+    <row r="92" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A92" s="28">
         <v>15</v>
       </c>
-      <c r="B92" s="38">
+      <c r="B92" s="28">
         <v>11</v>
       </c>
-      <c r="C92" s="32">
+      <c r="C92" s="22">
         <v>6</v>
       </c>
-      <c r="D92" s="32">
+      <c r="D92" s="22">
         <v>1170</v>
       </c>
-      <c r="E92" s="33" t="s">
+      <c r="E92" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F92" s="33" t="s">
+      <c r="F92" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G92" s="33"/>
-      <c r="H92" s="33"/>
-      <c r="I92" s="34" t="str">
+      <c r="G92" s="23"/>
+      <c r="H92" s="23"/>
+      <c r="I92" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 15 Hp, 11 Kw,  3 Phase
@@ -8599,10 +9076,10 @@
 Foot mounted - 160L  Frame
 TECO Brand</v>
       </c>
-      <c r="J92" s="34" t="s">
+      <c r="J92" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="K92" s="34" t="s">
+      <c r="K92" s="24" t="s">
         <v>72</v>
       </c>
       <c r="L92" s="5">
@@ -8642,28 +9119,28 @@
         <v>0.58799999999999997</v>
       </c>
     </row>
-    <row r="93" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="39">
+    <row r="93" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A93" s="29">
         <v>20</v>
       </c>
-      <c r="B93" s="39">
+      <c r="B93" s="29">
         <v>15</v>
       </c>
-      <c r="C93" s="36">
+      <c r="C93" s="26">
         <v>2</v>
       </c>
-      <c r="D93" s="36">
+      <c r="D93" s="26">
         <v>3520</v>
       </c>
-      <c r="E93" s="37" t="s">
+      <c r="E93" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="F93" s="33" t="s">
+      <c r="F93" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G93" s="33"/>
-      <c r="H93" s="33"/>
-      <c r="I93" s="34" t="str">
+      <c r="G93" s="23"/>
+      <c r="H93" s="23"/>
+      <c r="I93" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 20 Hp, 15 Kw,  3 Phase
@@ -8672,10 +9149,10 @@
 Foot mounted - 160M  Frame
 TECO Brand</v>
       </c>
-      <c r="J93" s="34" t="s">
+      <c r="J93" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="K93" s="34" t="s">
+      <c r="K93" s="24" t="s">
         <v>73</v>
       </c>
       <c r="L93" s="8">
@@ -8715,28 +9192,28 @@
         <v>0.183</v>
       </c>
     </row>
-    <row r="94" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="38">
+    <row r="94" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A94" s="28">
         <v>20</v>
       </c>
-      <c r="B94" s="38">
+      <c r="B94" s="28">
         <v>15</v>
       </c>
-      <c r="C94" s="32">
+      <c r="C94" s="22">
         <v>4</v>
       </c>
-      <c r="D94" s="32">
+      <c r="D94" s="22">
         <v>1760</v>
       </c>
-      <c r="E94" s="33" t="s">
+      <c r="E94" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F94" s="33" t="s">
+      <c r="F94" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G94" s="33"/>
-      <c r="H94" s="33"/>
-      <c r="I94" s="34" t="str">
+      <c r="G94" s="23"/>
+      <c r="H94" s="23"/>
+      <c r="I94" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 20 Hp, 15 Kw,  3 Phase
@@ -8745,10 +9222,10 @@
 Foot mounted - 160L  Frame
 TECO Brand</v>
       </c>
-      <c r="J94" s="34" t="s">
+      <c r="J94" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="K94" s="34" t="s">
+      <c r="K94" s="24" t="s">
         <v>74</v>
       </c>
       <c r="L94" s="5">
@@ -8788,28 +9265,28 @@
         <v>0.38100000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="39">
+    <row r="95" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A95" s="29">
         <v>20</v>
       </c>
-      <c r="B95" s="39">
+      <c r="B95" s="29">
         <v>15</v>
       </c>
-      <c r="C95" s="36">
+      <c r="C95" s="26">
         <v>6</v>
       </c>
-      <c r="D95" s="36">
+      <c r="D95" s="26">
         <v>1170</v>
       </c>
-      <c r="E95" s="37" t="s">
+      <c r="E95" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="F95" s="33" t="s">
+      <c r="F95" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G95" s="33"/>
-      <c r="H95" s="33"/>
-      <c r="I95" s="34" t="str">
+      <c r="G95" s="23"/>
+      <c r="H95" s="23"/>
+      <c r="I95" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 20 Hp, 15 Kw,  3 Phase
@@ -8818,10 +9295,10 @@
 Foot mounted - 180MC  Frame
 TECO Brand</v>
       </c>
-      <c r="J95" s="34" t="s">
+      <c r="J95" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="K95" s="34" t="s">
+      <c r="K95" s="24" t="s">
         <v>75</v>
       </c>
       <c r="L95" s="8">
@@ -8861,28 +9338,28 @@
         <v>1.054</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="38">
+    <row r="96" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A96" s="28">
         <v>25</v>
       </c>
-      <c r="B96" s="31">
+      <c r="B96" s="21">
         <v>18.5</v>
       </c>
-      <c r="C96" s="32">
+      <c r="C96" s="22">
         <v>2</v>
       </c>
-      <c r="D96" s="32">
+      <c r="D96" s="22">
         <v>3530</v>
       </c>
-      <c r="E96" s="33" t="s">
+      <c r="E96" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F96" s="33" t="s">
+      <c r="F96" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G96" s="33"/>
-      <c r="H96" s="33"/>
-      <c r="I96" s="34" t="str">
+      <c r="G96" s="23"/>
+      <c r="H96" s="23"/>
+      <c r="I96" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 25 Hp, 18.5 Kw,  3 Phase
@@ -8891,10 +9368,10 @@
 Foot mounted - 160L  Frame
 TECO Brand</v>
       </c>
-      <c r="J96" s="34" t="s">
+      <c r="J96" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="K96" s="34" t="s">
+      <c r="K96" s="24" t="s">
         <v>76</v>
       </c>
       <c r="L96" s="5">
@@ -8934,28 +9411,28 @@
         <v>0.23699999999999999</v>
       </c>
     </row>
-    <row r="97" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="39">
+    <row r="97" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A97" s="29">
         <v>25</v>
       </c>
-      <c r="B97" s="35">
+      <c r="B97" s="25">
         <v>18.5</v>
       </c>
-      <c r="C97" s="36">
+      <c r="C97" s="26">
         <v>4</v>
       </c>
-      <c r="D97" s="36">
+      <c r="D97" s="26">
         <v>1760</v>
       </c>
-      <c r="E97" s="37" t="s">
+      <c r="E97" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="F97" s="33" t="s">
+      <c r="F97" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G97" s="33"/>
-      <c r="H97" s="33"/>
-      <c r="I97" s="34" t="str">
+      <c r="G97" s="23"/>
+      <c r="H97" s="23"/>
+      <c r="I97" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 25 Hp, 18.5 Kw,  3 Phase
@@ -8964,10 +9441,10 @@
 Foot mounted - 180MC  Frame
 TECO Brand</v>
       </c>
-      <c r="J97" s="34" t="s">
+      <c r="J97" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="K97" s="34" t="s">
+      <c r="K97" s="24" t="s">
         <v>77</v>
       </c>
       <c r="L97" s="8">
@@ -9007,28 +9484,28 @@
         <v>0.57099999999999995</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="38">
+    <row r="98" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A98" s="28">
         <v>25</v>
       </c>
-      <c r="B98" s="31">
+      <c r="B98" s="21">
         <v>18.5</v>
       </c>
-      <c r="C98" s="32">
+      <c r="C98" s="22">
         <v>6</v>
       </c>
-      <c r="D98" s="32">
+      <c r="D98" s="22">
         <v>1170</v>
       </c>
-      <c r="E98" s="33" t="s">
+      <c r="E98" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="F98" s="33" t="s">
+      <c r="F98" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G98" s="33"/>
-      <c r="H98" s="33"/>
-      <c r="I98" s="34" t="str">
+      <c r="G98" s="23"/>
+      <c r="H98" s="23"/>
+      <c r="I98" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 25 Hp, 18.5 Kw,  3 Phase
@@ -9037,10 +9514,10 @@
 Foot mounted - 180LC  Frame
 TECO Brand</v>
       </c>
-      <c r="J98" s="34" t="s">
+      <c r="J98" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="K98" s="34" t="s">
+      <c r="K98" s="24" t="s">
         <v>78</v>
       </c>
       <c r="L98" s="5">
@@ -9080,28 +9557,28 @@
         <v>1.2330000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="39">
+    <row r="99" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A99" s="29">
         <v>30</v>
       </c>
-      <c r="B99" s="39">
+      <c r="B99" s="29">
         <v>22</v>
       </c>
-      <c r="C99" s="36">
+      <c r="C99" s="26">
         <v>2</v>
       </c>
-      <c r="D99" s="36">
+      <c r="D99" s="26">
         <v>3540</v>
       </c>
-      <c r="E99" s="37" t="s">
+      <c r="E99" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F99" s="33" t="s">
+      <c r="F99" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G99" s="33"/>
-      <c r="H99" s="33"/>
-      <c r="I99" s="34" t="str">
+      <c r="G99" s="23"/>
+      <c r="H99" s="23"/>
+      <c r="I99" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 30 Hp, 22 Kw,  3 Phase
@@ -9110,10 +9587,10 @@
 Foot mounted - 180MA  Frame
 TECO Brand</v>
       </c>
-      <c r="J99" s="34" t="s">
+      <c r="J99" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="K99" s="34" t="s">
+      <c r="K99" s="24" t="s">
         <v>79</v>
       </c>
       <c r="L99" s="8">
@@ -9153,28 +9630,28 @@
         <v>0.30199999999999999</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="38">
+    <row r="100" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A100" s="28">
         <v>30</v>
       </c>
-      <c r="B100" s="38">
+      <c r="B100" s="28">
         <v>22</v>
       </c>
-      <c r="C100" s="32">
+      <c r="C100" s="22">
         <v>4</v>
       </c>
-      <c r="D100" s="32">
+      <c r="D100" s="22">
         <v>1765</v>
       </c>
-      <c r="E100" s="33" t="s">
+      <c r="E100" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="F100" s="33" t="s">
+      <c r="F100" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G100" s="33"/>
-      <c r="H100" s="33"/>
-      <c r="I100" s="34" t="str">
+      <c r="G100" s="23"/>
+      <c r="H100" s="23"/>
+      <c r="I100" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 30 Hp, 22 Kw,  3 Phase
@@ -9183,10 +9660,10 @@
 Foot mounted - 180MC  Frame
 TECO Brand</v>
       </c>
-      <c r="J100" s="34" t="s">
+      <c r="J100" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="K100" s="34" t="s">
+      <c r="K100" s="24" t="s">
         <v>80</v>
       </c>
       <c r="L100" s="5">
@@ -9226,28 +9703,28 @@
         <v>0.70599999999999996</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="39">
+    <row r="101" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A101" s="29">
         <v>30</v>
       </c>
-      <c r="B101" s="39">
+      <c r="B101" s="29">
         <v>22</v>
       </c>
-      <c r="C101" s="36">
+      <c r="C101" s="26">
         <v>6</v>
       </c>
-      <c r="D101" s="36">
+      <c r="D101" s="26">
         <v>1175</v>
       </c>
-      <c r="E101" s="37" t="s">
+      <c r="E101" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="F101" s="33" t="s">
+      <c r="F101" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G101" s="33"/>
-      <c r="H101" s="33"/>
-      <c r="I101" s="34" t="str">
+      <c r="G101" s="23"/>
+      <c r="H101" s="23"/>
+      <c r="I101" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 30 Hp, 22 Kw,  3 Phase
@@ -9256,10 +9733,10 @@
 Foot mounted - 180LC  Frame
 TECO Brand</v>
       </c>
-      <c r="J101" s="34" t="s">
+      <c r="J101" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="K101" s="34" t="s">
+      <c r="K101" s="24" t="s">
         <v>81</v>
       </c>
       <c r="L101" s="8">
@@ -9299,28 +9776,28 @@
         <v>1.4379999999999999</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="38">
+    <row r="102" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A102" s="28">
         <v>40</v>
       </c>
-      <c r="B102" s="38">
+      <c r="B102" s="28">
         <v>30</v>
       </c>
-      <c r="C102" s="32">
+      <c r="C102" s="22">
         <v>2</v>
       </c>
-      <c r="D102" s="32">
+      <c r="D102" s="22">
         <v>3520</v>
       </c>
-      <c r="E102" s="33" t="s">
+      <c r="E102" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="F102" s="33" t="s">
+      <c r="F102" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G102" s="33"/>
-      <c r="H102" s="33"/>
-      <c r="I102" s="34" t="str">
+      <c r="G102" s="23"/>
+      <c r="H102" s="23"/>
+      <c r="I102" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 40 Hp, 30 Kw,  3 Phase
@@ -9329,10 +9806,10 @@
 Foot mounted - 180LA  Frame
 TECO Brand</v>
       </c>
-      <c r="J102" s="34" t="s">
+      <c r="J102" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="K102" s="34" t="s">
+      <c r="K102" s="24" t="s">
         <v>82</v>
       </c>
       <c r="L102" s="5">
@@ -9372,28 +9849,28 @@
         <v>0.35799999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="39">
+    <row r="103" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A103" s="29">
         <v>40</v>
       </c>
-      <c r="B103" s="39">
+      <c r="B103" s="29">
         <v>30</v>
       </c>
-      <c r="C103" s="36">
+      <c r="C103" s="26">
         <v>4</v>
       </c>
-      <c r="D103" s="36">
+      <c r="D103" s="26">
         <v>1760</v>
       </c>
-      <c r="E103" s="37" t="s">
+      <c r="E103" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="F103" s="33" t="s">
+      <c r="F103" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G103" s="33"/>
-      <c r="H103" s="33"/>
-      <c r="I103" s="34" t="str">
+      <c r="G103" s="23"/>
+      <c r="H103" s="23"/>
+      <c r="I103" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 40 Hp, 30 Kw,  3 Phase
@@ -9402,10 +9879,10 @@
 Foot mounted - 180LC  Frame
 TECO Brand</v>
       </c>
-      <c r="J103" s="34" t="s">
+      <c r="J103" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="K103" s="34" t="s">
+      <c r="K103" s="24" t="s">
         <v>83</v>
       </c>
       <c r="L103" s="8">
@@ -9445,28 +9922,28 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="104" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="38">
+    <row r="104" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A104" s="28">
         <v>40</v>
       </c>
-      <c r="B104" s="38">
+      <c r="B104" s="28">
         <v>30</v>
       </c>
-      <c r="C104" s="32">
+      <c r="C104" s="22">
         <v>6</v>
       </c>
-      <c r="D104" s="32">
+      <c r="D104" s="22">
         <v>1170</v>
       </c>
-      <c r="E104" s="33" t="s">
+      <c r="E104" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="F104" s="33" t="s">
+      <c r="F104" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G104" s="33"/>
-      <c r="H104" s="33"/>
-      <c r="I104" s="34" t="str">
+      <c r="G104" s="23"/>
+      <c r="H104" s="23"/>
+      <c r="I104" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 40 Hp, 30 Kw,  3 Phase
@@ -9475,10 +9952,10 @@
 Foot mounted - 200LC  Frame
 TECO Brand</v>
       </c>
-      <c r="J104" s="34" t="s">
+      <c r="J104" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="K104" s="34" t="s">
+      <c r="K104" s="24" t="s">
         <v>84</v>
       </c>
       <c r="L104" s="5">
@@ -9518,28 +9995,28 @@
         <v>1.919</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="39">
+    <row r="105" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A105" s="29">
         <v>50</v>
       </c>
-      <c r="B105" s="39">
+      <c r="B105" s="29">
         <v>37</v>
       </c>
-      <c r="C105" s="36">
+      <c r="C105" s="26">
         <v>2</v>
       </c>
-      <c r="D105" s="36">
+      <c r="D105" s="26">
         <v>3545</v>
       </c>
-      <c r="E105" s="37" t="s">
+      <c r="E105" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="F105" s="33" t="s">
+      <c r="F105" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G105" s="33"/>
-      <c r="H105" s="33"/>
-      <c r="I105" s="34" t="str">
+      <c r="G105" s="23"/>
+      <c r="H105" s="23"/>
+      <c r="I105" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 50 Hp, 37 Kw,  3 Phase
@@ -9548,10 +10025,10 @@
 Foot mounted - 200LA  Frame
 TECO Brand</v>
       </c>
-      <c r="J105" s="34" t="s">
+      <c r="J105" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="K105" s="34" t="s">
+      <c r="K105" s="24" t="s">
         <v>85</v>
       </c>
       <c r="L105" s="8">
@@ -9591,28 +10068,28 @@
         <v>0.60199999999999998</v>
       </c>
     </row>
-    <row r="106" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="38">
+    <row r="106" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A106" s="28">
         <v>50</v>
       </c>
-      <c r="B106" s="38">
+      <c r="B106" s="28">
         <v>37</v>
       </c>
-      <c r="C106" s="32">
+      <c r="C106" s="22">
         <v>4</v>
       </c>
-      <c r="D106" s="32">
+      <c r="D106" s="22">
         <v>1770</v>
       </c>
-      <c r="E106" s="33" t="s">
+      <c r="E106" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="F106" s="33" t="s">
+      <c r="F106" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G106" s="33"/>
-      <c r="H106" s="33"/>
-      <c r="I106" s="34" t="str">
+      <c r="G106" s="23"/>
+      <c r="H106" s="23"/>
+      <c r="I106" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 50 Hp, 37 Kw,  3 Phase
@@ -9621,10 +10098,10 @@
 Foot mounted - 200LC  Frame
 TECO Brand</v>
       </c>
-      <c r="J106" s="34" t="s">
+      <c r="J106" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="K106" s="34" t="s">
+      <c r="K106" s="24" t="s">
         <v>86</v>
       </c>
       <c r="L106" s="5">
@@ -9664,28 +10141,28 @@
         <v>1.4219999999999999</v>
       </c>
     </row>
-    <row r="107" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="39">
+    <row r="107" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A107" s="29">
         <v>50</v>
       </c>
-      <c r="B107" s="39">
+      <c r="B107" s="29">
         <v>37</v>
       </c>
-      <c r="C107" s="36">
+      <c r="C107" s="26">
         <v>6</v>
       </c>
-      <c r="D107" s="36">
+      <c r="D107" s="26">
         <v>1175</v>
       </c>
-      <c r="E107" s="37" t="s">
+      <c r="E107" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="F107" s="33" t="s">
+      <c r="F107" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G107" s="33"/>
-      <c r="H107" s="33"/>
-      <c r="I107" s="34" t="str">
+      <c r="G107" s="23"/>
+      <c r="H107" s="23"/>
+      <c r="I107" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 50 Hp, 37 Kw,  3 Phase
@@ -9694,10 +10171,10 @@
 Foot mounted - 200LC  Frame
 TECO Brand</v>
       </c>
-      <c r="J107" s="34" t="s">
+      <c r="J107" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="K107" s="34" t="s">
+      <c r="K107" s="24" t="s">
         <v>87</v>
       </c>
       <c r="L107" s="8">
@@ -9737,28 +10214,28 @@
         <v>2.419</v>
       </c>
     </row>
-    <row r="108" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="38">
+    <row r="108" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A108" s="28">
         <v>60</v>
       </c>
-      <c r="B108" s="38">
+      <c r="B108" s="28">
         <v>45</v>
       </c>
-      <c r="C108" s="32">
+      <c r="C108" s="22">
         <v>2</v>
       </c>
-      <c r="D108" s="32">
+      <c r="D108" s="22">
         <v>3545</v>
       </c>
-      <c r="E108" s="33" t="s">
+      <c r="E108" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="F108" s="33" t="s">
+      <c r="F108" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G108" s="33"/>
-      <c r="H108" s="33"/>
-      <c r="I108" s="34" t="str">
+      <c r="G108" s="23"/>
+      <c r="H108" s="23"/>
+      <c r="I108" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 60 Hp, 45 Kw,  3 Phase
@@ -9767,10 +10244,10 @@
 Foot mounted - 200LA  Frame
 TECO Brand</v>
       </c>
-      <c r="J108" s="34" t="s">
+      <c r="J108" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="K108" s="34" t="s">
+      <c r="K108" s="24" t="s">
         <v>88</v>
       </c>
       <c r="L108" s="5">
@@ -9810,28 +10287,28 @@
         <v>0.63300000000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="39">
+    <row r="109" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A109" s="29">
         <v>60</v>
       </c>
-      <c r="B109" s="39">
+      <c r="B109" s="29">
         <v>45</v>
       </c>
-      <c r="C109" s="36">
+      <c r="C109" s="26">
         <v>4</v>
       </c>
-      <c r="D109" s="36">
+      <c r="D109" s="26">
         <v>1765</v>
       </c>
-      <c r="E109" s="37" t="s">
+      <c r="E109" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="F109" s="33" t="s">
+      <c r="F109" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G109" s="33"/>
-      <c r="H109" s="33"/>
-      <c r="I109" s="34" t="str">
+      <c r="G109" s="23"/>
+      <c r="H109" s="23"/>
+      <c r="I109" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 60 Hp, 45 Kw,  3 Phase
@@ -9840,10 +10317,10 @@
 Foot mounted - 200LC  Frame
 TECO Brand</v>
       </c>
-      <c r="J109" s="34" t="s">
+      <c r="J109" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="K109" s="34" t="s">
+      <c r="K109" s="24" t="s">
         <v>89</v>
       </c>
       <c r="L109" s="8">
@@ -9883,28 +10360,28 @@
         <v>1.643</v>
       </c>
     </row>
-    <row r="110" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="38">
+    <row r="110" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A110" s="28">
         <v>60</v>
       </c>
-      <c r="B110" s="38">
+      <c r="B110" s="28">
         <v>45</v>
       </c>
-      <c r="C110" s="32">
+      <c r="C110" s="22">
         <v>6</v>
       </c>
-      <c r="D110" s="32">
+      <c r="D110" s="22">
         <v>1180</v>
       </c>
-      <c r="E110" s="33" t="s">
+      <c r="E110" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F110" s="33" t="s">
+      <c r="F110" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G110" s="33"/>
-      <c r="H110" s="33"/>
-      <c r="I110" s="34" t="str">
+      <c r="G110" s="23"/>
+      <c r="H110" s="23"/>
+      <c r="I110" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 60 Hp, 45 Kw,  3 Phase
@@ -9913,10 +10390,10 @@
 Foot mounted - 225SC  Frame
 TECO Brand</v>
       </c>
-      <c r="J110" s="34" t="s">
+      <c r="J110" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="K110" s="34" t="s">
+      <c r="K110" s="24" t="s">
         <v>90</v>
       </c>
       <c r="L110" s="5">
@@ -9956,28 +10433,28 @@
         <v>3.0230000000000001</v>
       </c>
     </row>
-    <row r="111" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="39">
+    <row r="111" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A111" s="29">
         <v>75</v>
       </c>
-      <c r="B111" s="39">
+      <c r="B111" s="29">
         <v>55</v>
       </c>
-      <c r="C111" s="36">
+      <c r="C111" s="26">
         <v>2</v>
       </c>
-      <c r="D111" s="36">
+      <c r="D111" s="26">
         <v>3550</v>
       </c>
-      <c r="E111" s="37" t="s">
+      <c r="E111" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="F111" s="33" t="s">
+      <c r="F111" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G111" s="33"/>
-      <c r="H111" s="33"/>
-      <c r="I111" s="34" t="str">
+      <c r="G111" s="23"/>
+      <c r="H111" s="23"/>
+      <c r="I111" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 75 Hp, 55 Kw,  3 Phase
@@ -9986,10 +10463,10 @@
 Foot mounted - 225SA  Frame
 TECO Brand</v>
       </c>
-      <c r="J111" s="34" t="s">
+      <c r="J111" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="K111" s="34" t="s">
+      <c r="K111" s="24" t="s">
         <v>91</v>
       </c>
       <c r="L111" s="8">
@@ -10029,28 +10506,28 @@
         <v>1.1870000000000001</v>
       </c>
     </row>
-    <row r="112" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="38">
+    <row r="112" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A112" s="28">
         <v>75</v>
       </c>
-      <c r="B112" s="38">
+      <c r="B112" s="28">
         <v>55</v>
       </c>
-      <c r="C112" s="32">
+      <c r="C112" s="22">
         <v>4</v>
       </c>
-      <c r="D112" s="32">
+      <c r="D112" s="22">
         <v>1775</v>
       </c>
-      <c r="E112" s="33" t="s">
+      <c r="E112" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F112" s="33" t="s">
+      <c r="F112" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G112" s="33"/>
-      <c r="H112" s="33"/>
-      <c r="I112" s="34" t="str">
+      <c r="G112" s="23"/>
+      <c r="H112" s="23"/>
+      <c r="I112" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 75 Hp, 55 Kw,  3 Phase
@@ -10059,10 +10536,10 @@
 Foot mounted - 225SC  Frame
 TECO Brand</v>
       </c>
-      <c r="J112" s="34" t="s">
+      <c r="J112" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="K112" s="34" t="s">
+      <c r="K112" s="24" t="s">
         <v>92</v>
       </c>
       <c r="L112" s="5">
@@ -10102,28 +10579,28 @@
         <v>1.9790000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="39">
+    <row r="113" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A113" s="29">
         <v>75</v>
       </c>
-      <c r="B113" s="39">
+      <c r="B113" s="29">
         <v>55</v>
       </c>
-      <c r="C113" s="36">
+      <c r="C113" s="26">
         <v>6</v>
       </c>
-      <c r="D113" s="36">
+      <c r="D113" s="26">
         <v>1175</v>
       </c>
-      <c r="E113" s="37" t="s">
+      <c r="E113" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="F113" s="33" t="s">
+      <c r="F113" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G113" s="33"/>
-      <c r="H113" s="33"/>
-      <c r="I113" s="34" t="str">
+      <c r="G113" s="23"/>
+      <c r="H113" s="23"/>
+      <c r="I113" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 75 Hp, 55 Kw,  3 Phase
@@ -10132,10 +10609,10 @@
 Foot mounted - A250SC  Frame
 TECO Brand</v>
       </c>
-      <c r="J113" s="34" t="s">
+      <c r="J113" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="K113" s="34" t="s">
+      <c r="K113" s="24" t="s">
         <v>93</v>
       </c>
       <c r="L113" s="8">
@@ -10175,28 +10652,28 @@
         <v>4.923</v>
       </c>
     </row>
-    <row r="114" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="39">
+    <row r="114" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A114" s="29">
         <v>100</v>
       </c>
-      <c r="B114" s="39">
+      <c r="B114" s="29">
         <v>75</v>
       </c>
-      <c r="C114" s="36">
+      <c r="C114" s="26">
         <v>2</v>
       </c>
-      <c r="D114" s="36">
+      <c r="D114" s="26">
         <v>3550</v>
       </c>
-      <c r="E114" s="37" t="s">
+      <c r="E114" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="F114" s="33" t="s">
+      <c r="F114" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G114" s="33"/>
-      <c r="H114" s="33"/>
-      <c r="I114" s="34" t="str">
+      <c r="G114" s="23"/>
+      <c r="H114" s="23"/>
+      <c r="I114" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 100 Hp, 75 Kw,  3 Phase
@@ -10205,10 +10682,10 @@
 Foot mounted - A250SA  Frame
 TECO Brand</v>
       </c>
-      <c r="J114" s="34" t="s">
+      <c r="J114" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="K114" s="34" t="s">
+      <c r="K114" s="24" t="s">
         <v>94</v>
       </c>
       <c r="L114" s="8">
@@ -10248,28 +10725,28 @@
         <v>1.6779999999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="38">
+    <row r="115" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A115" s="28">
         <v>100</v>
       </c>
-      <c r="B115" s="38">
+      <c r="B115" s="28">
         <v>75</v>
       </c>
-      <c r="C115" s="32">
+      <c r="C115" s="22">
         <v>4</v>
       </c>
-      <c r="D115" s="32">
+      <c r="D115" s="22">
         <v>1775</v>
       </c>
-      <c r="E115" s="33" t="s">
+      <c r="E115" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="F115" s="33" t="s">
+      <c r="F115" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G115" s="33"/>
-      <c r="H115" s="33"/>
-      <c r="I115" s="34" t="str">
+      <c r="G115" s="23"/>
+      <c r="H115" s="23"/>
+      <c r="I115" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 100 Hp, 75 Kw,  3 Phase
@@ -10278,10 +10755,10 @@
 Foot mounted - A250SC  Frame
 TECO Brand</v>
       </c>
-      <c r="J115" s="34" t="s">
+      <c r="J115" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="K115" s="34" t="s">
+      <c r="K115" s="24" t="s">
         <v>95</v>
       </c>
       <c r="L115" s="5">
@@ -10321,28 +10798,28 @@
         <v>4.226</v>
       </c>
     </row>
-    <row r="116" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="39">
+    <row r="116" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A116" s="29">
         <v>100</v>
       </c>
-      <c r="B116" s="39">
+      <c r="B116" s="29">
         <v>75</v>
       </c>
-      <c r="C116" s="36">
+      <c r="C116" s="26">
         <v>6</v>
       </c>
-      <c r="D116" s="36">
+      <c r="D116" s="26">
         <v>1175</v>
       </c>
-      <c r="E116" s="37" t="s">
+      <c r="E116" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="F116" s="33" t="s">
+      <c r="F116" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G116" s="33"/>
-      <c r="H116" s="33"/>
-      <c r="I116" s="34" t="str">
+      <c r="G116" s="23"/>
+      <c r="H116" s="23"/>
+      <c r="I116" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 100 Hp, 75 Kw,  3 Phase
@@ -10351,10 +10828,10 @@
 Foot mounted - A250MC  Frame
 TECO Brand</v>
       </c>
-      <c r="J116" s="34" t="s">
+      <c r="J116" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="K116" s="34" t="s">
+      <c r="K116" s="24" t="s">
         <v>96</v>
       </c>
       <c r="L116" s="8">
@@ -10394,28 +10871,28 @@
         <v>6.3819999999999997</v>
       </c>
     </row>
-    <row r="117" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="39">
+    <row r="117" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A117" s="29">
         <v>125</v>
       </c>
-      <c r="B117" s="39">
+      <c r="B117" s="29">
         <v>90</v>
       </c>
-      <c r="C117" s="36">
+      <c r="C117" s="26">
         <v>2</v>
       </c>
-      <c r="D117" s="36">
+      <c r="D117" s="26">
         <v>3555</v>
       </c>
-      <c r="E117" s="37" t="s">
+      <c r="E117" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="F117" s="33" t="s">
+      <c r="F117" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G117" s="33"/>
-      <c r="H117" s="33"/>
-      <c r="I117" s="34" t="str">
+      <c r="G117" s="23"/>
+      <c r="H117" s="23"/>
+      <c r="I117" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 125 Hp, 90 Kw,  3 Phase
@@ -10424,10 +10901,10 @@
 Foot mounted - A250MA  Frame
 TECO Brand</v>
       </c>
-      <c r="J117" s="34" t="s">
+      <c r="J117" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="K117" s="34" t="s">
+      <c r="K117" s="24" t="s">
         <v>97</v>
       </c>
       <c r="L117" s="8">
@@ -10467,28 +10944,28 @@
         <v>2.0139999999999998</v>
       </c>
     </row>
-    <row r="118" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="38">
+    <row r="118" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A118" s="28">
         <v>125</v>
       </c>
-      <c r="B118" s="38">
+      <c r="B118" s="28">
         <v>90</v>
       </c>
-      <c r="C118" s="32">
+      <c r="C118" s="22">
         <v>4</v>
       </c>
-      <c r="D118" s="32">
+      <c r="D118" s="22">
         <v>1770</v>
       </c>
-      <c r="E118" s="33" t="s">
+      <c r="E118" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F118" s="33" t="s">
+      <c r="F118" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G118" s="33"/>
-      <c r="H118" s="33"/>
-      <c r="I118" s="34" t="str">
+      <c r="G118" s="23"/>
+      <c r="H118" s="23"/>
+      <c r="I118" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 125 Hp, 90 Kw,  3 Phase
@@ -10497,10 +10974,10 @@
 Foot mounted - A250MC  Frame
 TECO Brand</v>
       </c>
-      <c r="J118" s="34" t="s">
+      <c r="J118" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="K118" s="34" t="s">
+      <c r="K118" s="24" t="s">
         <v>98</v>
       </c>
       <c r="L118" s="5">
@@ -10540,28 +11017,28 @@
         <v>5.101</v>
       </c>
     </row>
-    <row r="119" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="39">
+    <row r="119" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A119" s="29">
         <v>125</v>
       </c>
-      <c r="B119" s="39">
+      <c r="B119" s="29">
         <v>90</v>
       </c>
-      <c r="C119" s="36">
+      <c r="C119" s="26">
         <v>6</v>
       </c>
-      <c r="D119" s="36">
+      <c r="D119" s="26">
         <v>1180</v>
       </c>
-      <c r="E119" s="37" t="s">
+      <c r="E119" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="F119" s="33" t="s">
+      <c r="F119" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G119" s="33"/>
-      <c r="H119" s="33"/>
-      <c r="I119" s="34" t="str">
+      <c r="G119" s="23"/>
+      <c r="H119" s="23"/>
+      <c r="I119" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 125 Hp, 90 Kw,  3 Phase
@@ -10570,10 +11047,10 @@
 Foot mounted - 280S  Frame
 TECO Brand</v>
       </c>
-      <c r="J119" s="34" t="s">
+      <c r="J119" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="K119" s="34" t="s">
+      <c r="K119" s="24" t="s">
         <v>99</v>
       </c>
       <c r="L119" s="8">
@@ -10613,28 +11090,28 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="120" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="39">
+    <row r="120" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A120" s="29">
         <v>150</v>
       </c>
-      <c r="B120" s="39">
+      <c r="B120" s="29">
         <v>110</v>
       </c>
-      <c r="C120" s="36">
+      <c r="C120" s="26">
         <v>2</v>
       </c>
-      <c r="D120" s="36">
+      <c r="D120" s="26">
         <v>3565</v>
       </c>
-      <c r="E120" s="37" t="s">
+      <c r="E120" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="F120" s="33" t="s">
+      <c r="F120" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G120" s="33"/>
-      <c r="H120" s="33"/>
-      <c r="I120" s="34" t="str">
+      <c r="G120" s="23"/>
+      <c r="H120" s="23"/>
+      <c r="I120" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 150 Hp, 110 Kw,  3 Phase
@@ -10643,10 +11120,10 @@
 Foot mounted - 280S  Frame
 TECO Brand</v>
       </c>
-      <c r="J120" s="34" t="s">
+      <c r="J120" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="K120" s="34" t="s">
+      <c r="K120" s="24" t="s">
         <v>100</v>
       </c>
       <c r="L120" s="8">
@@ -10686,28 +11163,28 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="38">
+    <row r="121" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A121" s="28">
         <v>150</v>
       </c>
-      <c r="B121" s="38">
+      <c r="B121" s="28">
         <v>110</v>
       </c>
-      <c r="C121" s="32">
+      <c r="C121" s="22">
         <v>4</v>
       </c>
-      <c r="D121" s="32">
+      <c r="D121" s="22">
         <v>1770</v>
       </c>
-      <c r="E121" s="33" t="s">
+      <c r="E121" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="F121" s="33" t="s">
+      <c r="F121" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G121" s="33"/>
-      <c r="H121" s="33"/>
-      <c r="I121" s="34" t="str">
+      <c r="G121" s="23"/>
+      <c r="H121" s="23"/>
+      <c r="I121" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 150 Hp, 110 Kw,  3 Phase
@@ -10716,10 +11193,10 @@
 Foot mounted - 280S  Frame
 TECO Brand</v>
       </c>
-      <c r="J121" s="34" t="s">
+      <c r="J121" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="K121" s="34" t="s">
+      <c r="K121" s="24" t="s">
         <v>101</v>
       </c>
       <c r="L121" s="5">
@@ -10759,28 +11236,28 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="122" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="39">
+    <row r="122" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A122" s="29">
         <v>150</v>
       </c>
-      <c r="B122" s="39">
+      <c r="B122" s="29">
         <v>110</v>
       </c>
-      <c r="C122" s="36">
+      <c r="C122" s="26">
         <v>6</v>
       </c>
-      <c r="D122" s="36">
+      <c r="D122" s="26">
         <v>1180</v>
       </c>
-      <c r="E122" s="37" t="s">
+      <c r="E122" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="F122" s="33" t="s">
+      <c r="F122" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G122" s="33"/>
-      <c r="H122" s="33"/>
-      <c r="I122" s="34" t="str">
+      <c r="G122" s="23"/>
+      <c r="H122" s="23"/>
+      <c r="I122" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 150 Hp, 110 Kw,  3 Phase
@@ -10789,10 +11266,10 @@
 Foot mounted - 280M  Frame
 TECO Brand</v>
       </c>
-      <c r="J122" s="34" t="s">
+      <c r="J122" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="K122" s="34" t="s">
+      <c r="K122" s="24" t="s">
         <v>102</v>
       </c>
       <c r="L122" s="8">
@@ -10832,28 +11309,28 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="123" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="39">
+    <row r="123" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A123" s="29">
         <v>175</v>
       </c>
-      <c r="B123" s="39">
+      <c r="B123" s="29">
         <v>132</v>
       </c>
-      <c r="C123" s="36">
+      <c r="C123" s="26">
         <v>2</v>
       </c>
-      <c r="D123" s="36">
+      <c r="D123" s="26">
         <v>3565</v>
       </c>
-      <c r="E123" s="37" t="s">
+      <c r="E123" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="F123" s="33" t="s">
+      <c r="F123" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G123" s="33"/>
-      <c r="H123" s="33"/>
-      <c r="I123" s="34" t="str">
+      <c r="G123" s="23"/>
+      <c r="H123" s="23"/>
+      <c r="I123" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 175 Hp, 132 Kw,  3 Phase
@@ -10862,10 +11339,10 @@
 Foot mounted - 280M  Frame
 TECO Brand</v>
       </c>
-      <c r="J123" s="34" t="s">
+      <c r="J123" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="K123" s="34" t="s">
+      <c r="K123" s="24" t="s">
         <v>103</v>
       </c>
       <c r="L123" s="8">
@@ -10905,28 +11382,28 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="124" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="38">
+    <row r="124" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A124" s="28">
         <v>175</v>
       </c>
-      <c r="B124" s="38">
+      <c r="B124" s="28">
         <v>132</v>
       </c>
-      <c r="C124" s="32">
+      <c r="C124" s="22">
         <v>4</v>
       </c>
-      <c r="D124" s="32">
+      <c r="D124" s="22">
         <v>1770</v>
       </c>
-      <c r="E124" s="33" t="s">
+      <c r="E124" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="F124" s="33" t="s">
+      <c r="F124" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G124" s="33"/>
-      <c r="H124" s="33"/>
-      <c r="I124" s="34" t="str">
+      <c r="G124" s="23"/>
+      <c r="H124" s="23"/>
+      <c r="I124" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 175 Hp, 132 Kw,  3 Phase
@@ -10935,10 +11412,10 @@
 Foot mounted - 280M  Frame
 TECO Brand</v>
       </c>
-      <c r="J124" s="34" t="s">
+      <c r="J124" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="K124" s="34" t="s">
+      <c r="K124" s="24" t="s">
         <v>104</v>
       </c>
       <c r="L124" s="5">
@@ -10978,28 +11455,28 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="125" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="39">
+    <row r="125" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A125" s="29">
         <v>175</v>
       </c>
-      <c r="B125" s="39">
+      <c r="B125" s="29">
         <v>132</v>
       </c>
-      <c r="C125" s="36">
+      <c r="C125" s="26">
         <v>6</v>
       </c>
-      <c r="D125" s="36">
+      <c r="D125" s="26">
         <v>1185</v>
       </c>
-      <c r="E125" s="37" t="s">
+      <c r="E125" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="F125" s="33" t="s">
+      <c r="F125" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G125" s="33"/>
-      <c r="H125" s="33"/>
-      <c r="I125" s="34" t="str">
+      <c r="G125" s="23"/>
+      <c r="H125" s="23"/>
+      <c r="I125" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 175 Hp, 132 Kw,  3 Phase
@@ -11008,10 +11485,10 @@
 Foot mounted - 315S  Frame
 TECO Brand</v>
       </c>
-      <c r="J125" s="34" t="s">
+      <c r="J125" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="K125" s="34" t="s">
+      <c r="K125" s="24" t="s">
         <v>105</v>
       </c>
       <c r="L125" s="8">
@@ -11051,28 +11528,28 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="126" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="38">
+    <row r="126" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A126" s="28">
         <v>200</v>
       </c>
-      <c r="B126" s="38">
+      <c r="B126" s="28">
         <v>160</v>
       </c>
-      <c r="C126" s="32">
+      <c r="C126" s="22">
         <v>2</v>
       </c>
-      <c r="D126" s="32">
+      <c r="D126" s="22">
         <v>3570</v>
       </c>
-      <c r="E126" s="33" t="s">
+      <c r="E126" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="F126" s="33" t="s">
+      <c r="F126" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G126" s="33"/>
-      <c r="H126" s="33"/>
-      <c r="I126" s="34" t="str">
+      <c r="G126" s="23"/>
+      <c r="H126" s="23"/>
+      <c r="I126" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 200 Hp, 160 Kw,  3 Phase
@@ -11081,10 +11558,10 @@
 Foot mounted - 315S  Frame
 TECO Brand</v>
       </c>
-      <c r="J126" s="34" t="s">
+      <c r="J126" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="K126" s="34" t="s">
+      <c r="K126" s="24" t="s">
         <v>106</v>
       </c>
       <c r="L126" s="5">
@@ -11124,28 +11601,28 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="127" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="39">
+    <row r="127" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A127" s="29">
         <v>200</v>
       </c>
-      <c r="B127" s="39">
+      <c r="B127" s="29">
         <v>160</v>
       </c>
-      <c r="C127" s="36">
+      <c r="C127" s="26">
         <v>4</v>
       </c>
-      <c r="D127" s="36">
+      <c r="D127" s="26">
         <v>1775</v>
       </c>
-      <c r="E127" s="37" t="s">
+      <c r="E127" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="F127" s="33" t="s">
+      <c r="F127" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G127" s="33"/>
-      <c r="H127" s="33"/>
-      <c r="I127" s="34" t="str">
+      <c r="G127" s="23"/>
+      <c r="H127" s="23"/>
+      <c r="I127" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 200 Hp, 160 Kw,  3 Phase
@@ -11154,10 +11631,10 @@
 Foot mounted - 315S  Frame
 TECO Brand</v>
       </c>
-      <c r="J127" s="34" t="s">
+      <c r="J127" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="K127" s="34" t="s">
+      <c r="K127" s="24" t="s">
         <v>107</v>
       </c>
       <c r="L127" s="8">
@@ -11197,28 +11674,28 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="128" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="38">
+    <row r="128" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A128" s="28">
         <v>200</v>
       </c>
-      <c r="B128" s="38">
+      <c r="B128" s="28">
         <v>160</v>
       </c>
-      <c r="C128" s="32">
+      <c r="C128" s="22">
         <v>6</v>
       </c>
-      <c r="D128" s="32">
+      <c r="D128" s="22">
         <v>1185</v>
       </c>
-      <c r="E128" s="33" t="s">
+      <c r="E128" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F128" s="33" t="s">
+      <c r="F128" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G128" s="33"/>
-      <c r="H128" s="33"/>
-      <c r="I128" s="34" t="str">
+      <c r="G128" s="23"/>
+      <c r="H128" s="23"/>
+      <c r="I128" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 200 Hp, 160 Kw,  3 Phase
@@ -11227,10 +11704,10 @@
 Foot mounted - 315M  Frame
 TECO Brand</v>
       </c>
-      <c r="J128" s="34" t="s">
+      <c r="J128" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="K128" s="34" t="s">
+      <c r="K128" s="24" t="s">
         <v>108</v>
       </c>
       <c r="L128" s="5">
@@ -11270,28 +11747,28 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="129" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="39">
+    <row r="129" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A129" s="29">
         <v>250</v>
       </c>
-      <c r="B129" s="39">
+      <c r="B129" s="29">
         <v>200</v>
       </c>
-      <c r="C129" s="36">
+      <c r="C129" s="26">
         <v>2</v>
       </c>
-      <c r="D129" s="36">
+      <c r="D129" s="26">
         <v>3570</v>
       </c>
-      <c r="E129" s="37" t="s">
+      <c r="E129" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="F129" s="33" t="s">
+      <c r="F129" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G129" s="33"/>
-      <c r="H129" s="33"/>
-      <c r="I129" s="34" t="str">
+      <c r="G129" s="23"/>
+      <c r="H129" s="23"/>
+      <c r="I129" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 250 Hp, 200 Kw,  3 Phase
@@ -11300,10 +11777,10 @@
 Foot mounted - 315M  Frame
 TECO Brand</v>
       </c>
-      <c r="J129" s="34" t="s">
+      <c r="J129" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="K129" s="34" t="s">
+      <c r="K129" s="24" t="s">
         <v>109</v>
       </c>
       <c r="L129" s="8">
@@ -11343,28 +11820,28 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="130" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="38">
+    <row r="130" spans="1:23" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A130" s="28">
         <v>250</v>
       </c>
-      <c r="B130" s="38">
+      <c r="B130" s="28">
         <v>200</v>
       </c>
-      <c r="C130" s="32">
+      <c r="C130" s="22">
         <v>4</v>
       </c>
-      <c r="D130" s="32">
+      <c r="D130" s="22">
         <v>1775</v>
       </c>
-      <c r="E130" s="33" t="s">
+      <c r="E130" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F130" s="33" t="s">
+      <c r="F130" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G130" s="33"/>
-      <c r="H130" s="33"/>
-      <c r="I130" s="34" t="str">
+      <c r="G130" s="23"/>
+      <c r="H130" s="23"/>
+      <c r="I130" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Induction motor - TEFC
 250 Hp, 200 Kw,  3 Phase
@@ -11373,10 +11850,10 @@
 Foot mounted - 315M  Frame
 TECO Brand</v>
       </c>
-      <c r="J130" s="34" t="s">
+      <c r="J130" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="K130" s="34" t="s">
+      <c r="K130" s="24" t="s">
         <v>110</v>
       </c>
       <c r="L130" s="5">
@@ -11445,10 +11922,2338 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC69F5C3-F127-42CC-9EE4-1D15C15CDA32}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE305384-A95D-4E9E-8E48-214A0B541C7B}">
+  <dimension ref="A1:W37"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="2" width="8" customWidth="1"/>
+    <col min="3" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="12.86328125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="12" hidden="1" customWidth="1"/>
+    <col min="9" max="10" width="62.59765625" customWidth="1"/>
+    <col min="11" max="18" width="11" hidden="1" customWidth="1"/>
+    <col min="19" max="22" width="14" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+    </row>
+    <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+    </row>
+    <row r="4" spans="1:22" ht="27.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="I4" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="R4" s="30"/>
+      <c r="S4" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="T4" s="30"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V5" s="30"/>
+    </row>
+    <row r="6" spans="1:22" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+    </row>
+    <row r="7" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="B7" s="14">
+        <v>0.37</v>
+      </c>
+      <c r="C7" s="15">
+        <v>4</v>
+      </c>
+      <c r="D7" s="15">
+        <v>1596</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="17">
+        <v>10990</v>
+      </c>
+      <c r="H7" s="18">
+        <f>G7*1.3</f>
+        <v>14287</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5">
+        <v>77</v>
+      </c>
+      <c r="O7" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P7" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>1</v>
+      </c>
+      <c r="R7" s="3">
+        <v>6</v>
+      </c>
+      <c r="S7" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T7" s="3">
+        <v>400</v>
+      </c>
+      <c r="U7" s="3">
+        <v>370</v>
+      </c>
+      <c r="V7" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="B8" s="14">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C8" s="15">
+        <v>4</v>
+      </c>
+      <c r="D8" s="15">
+        <v>1668</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="17">
+        <v>12822</v>
+      </c>
+      <c r="H8" s="18">
+        <f t="shared" ref="H8:H14" si="0">G8*1.3</f>
+        <v>16668.600000000002</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5">
+        <v>77</v>
+      </c>
+      <c r="O8" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P8" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>1</v>
+      </c>
+      <c r="R8" s="3">
+        <v>6</v>
+      </c>
+      <c r="S8" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T8" s="3">
+        <v>400</v>
+      </c>
+      <c r="U8" s="3">
+        <v>370</v>
+      </c>
+      <c r="V8" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="14">
+        <v>1</v>
+      </c>
+      <c r="B9" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C9" s="15">
+        <v>4</v>
+      </c>
+      <c r="D9" s="15">
+        <v>1668</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="17">
+        <v>15617</v>
+      </c>
+      <c r="H9" s="18">
+        <f t="shared" si="0"/>
+        <v>20302.100000000002</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5">
+        <v>77</v>
+      </c>
+      <c r="O9" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P9" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>1</v>
+      </c>
+      <c r="R9" s="3">
+        <v>6</v>
+      </c>
+      <c r="S9" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T9" s="3">
+        <v>400</v>
+      </c>
+      <c r="U9" s="3">
+        <v>370</v>
+      </c>
+      <c r="V9" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="B10" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C10" s="15">
+        <v>4</v>
+      </c>
+      <c r="D10" s="15">
+        <v>1668</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="17">
+        <v>19472</v>
+      </c>
+      <c r="H10" s="18">
+        <f t="shared" si="0"/>
+        <v>25313.600000000002</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5">
+        <v>77</v>
+      </c>
+      <c r="O10" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P10" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>1</v>
+      </c>
+      <c r="R10" s="3">
+        <v>6</v>
+      </c>
+      <c r="S10" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T10" s="3">
+        <v>400</v>
+      </c>
+      <c r="U10" s="3">
+        <v>370</v>
+      </c>
+      <c r="V10" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="14">
+        <v>2</v>
+      </c>
+      <c r="B11" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="15">
+        <v>4</v>
+      </c>
+      <c r="D11" s="15">
+        <v>1668</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="17">
+        <v>21015</v>
+      </c>
+      <c r="H11" s="18">
+        <f t="shared" si="0"/>
+        <v>27319.5</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5">
+        <v>77</v>
+      </c>
+      <c r="O11" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P11" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3">
+        <v>6</v>
+      </c>
+      <c r="S11" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T11" s="3">
+        <v>400</v>
+      </c>
+      <c r="U11" s="3">
+        <v>370</v>
+      </c>
+      <c r="V11" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="14">
+        <v>3</v>
+      </c>
+      <c r="B12" s="14">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C12" s="15">
+        <v>4</v>
+      </c>
+      <c r="D12" s="15">
+        <v>1668</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="17">
+        <v>24678</v>
+      </c>
+      <c r="H12" s="18">
+        <f t="shared" si="0"/>
+        <v>32081.4</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5">
+        <v>77</v>
+      </c>
+      <c r="O12" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P12" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>1</v>
+      </c>
+      <c r="R12" s="3">
+        <v>6</v>
+      </c>
+      <c r="S12" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T12" s="3">
+        <v>400</v>
+      </c>
+      <c r="U12" s="3">
+        <v>370</v>
+      </c>
+      <c r="V12" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="14">
+        <v>5.5</v>
+      </c>
+      <c r="B13" s="14">
+        <v>4</v>
+      </c>
+      <c r="C13" s="15">
+        <v>4</v>
+      </c>
+      <c r="D13" s="15">
+        <v>1692</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="17">
+        <v>30656</v>
+      </c>
+      <c r="H13" s="18">
+        <f t="shared" si="0"/>
+        <v>39852.800000000003</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5">
+        <v>77</v>
+      </c>
+      <c r="O13" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P13" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>1</v>
+      </c>
+      <c r="R13" s="3">
+        <v>6</v>
+      </c>
+      <c r="S13" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T13" s="3">
+        <v>400</v>
+      </c>
+      <c r="U13" s="3">
+        <v>370</v>
+      </c>
+      <c r="V13" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="B14" s="14">
+        <v>5.5</v>
+      </c>
+      <c r="C14" s="15">
+        <v>4</v>
+      </c>
+      <c r="D14" s="15">
+        <v>1722</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="17">
+        <v>34030</v>
+      </c>
+      <c r="H14" s="18">
+        <f t="shared" si="0"/>
+        <v>44239</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5">
+        <v>77</v>
+      </c>
+      <c r="O14" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P14" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>1</v>
+      </c>
+      <c r="R14" s="3">
+        <v>6</v>
+      </c>
+      <c r="S14" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T14" s="3">
+        <v>400</v>
+      </c>
+      <c r="U14" s="3">
+        <v>370</v>
+      </c>
+      <c r="V14" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="14">
+        <v>10</v>
+      </c>
+      <c r="B15" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="C15" s="15">
+        <v>4</v>
+      </c>
+      <c r="D15" s="15">
+        <v>1728</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="17">
+        <v>10990</v>
+      </c>
+      <c r="H15" s="18">
+        <f>G15*1.3</f>
+        <v>14287</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5">
+        <v>77</v>
+      </c>
+      <c r="O15" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P15" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>1</v>
+      </c>
+      <c r="R15" s="3">
+        <v>6</v>
+      </c>
+      <c r="S15" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T15" s="3">
+        <v>400</v>
+      </c>
+      <c r="U15" s="3">
+        <v>370</v>
+      </c>
+      <c r="V15" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="14">
+        <v>10</v>
+      </c>
+      <c r="B16" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="C16" s="15">
+        <v>2</v>
+      </c>
+      <c r="D16" s="15">
+        <v>3480</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="17">
+        <v>12822</v>
+      </c>
+      <c r="H16" s="18">
+        <f t="shared" ref="H16:H22" si="1">G16*1.3</f>
+        <v>16668.600000000002</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5">
+        <v>77</v>
+      </c>
+      <c r="O16" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P16" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>1</v>
+      </c>
+      <c r="R16" s="3">
+        <v>6</v>
+      </c>
+      <c r="S16" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T16" s="3">
+        <v>400</v>
+      </c>
+      <c r="U16" s="3">
+        <v>370</v>
+      </c>
+      <c r="V16" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="14">
+        <v>15</v>
+      </c>
+      <c r="B17" s="14">
+        <v>11</v>
+      </c>
+      <c r="C17" s="15">
+        <v>4</v>
+      </c>
+      <c r="D17" s="15">
+        <v>1728</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="17">
+        <v>15617</v>
+      </c>
+      <c r="H17" s="18">
+        <f t="shared" si="1"/>
+        <v>20302.100000000002</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5">
+        <v>77</v>
+      </c>
+      <c r="O17" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P17" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>1</v>
+      </c>
+      <c r="R17" s="3">
+        <v>6</v>
+      </c>
+      <c r="S17" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T17" s="3">
+        <v>400</v>
+      </c>
+      <c r="U17" s="3">
+        <v>370</v>
+      </c>
+      <c r="V17" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="14">
+        <v>20</v>
+      </c>
+      <c r="B18" s="14">
+        <v>15</v>
+      </c>
+      <c r="C18" s="15">
+        <v>4</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1752</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="17">
+        <v>19472</v>
+      </c>
+      <c r="H18" s="18">
+        <f t="shared" si="1"/>
+        <v>25313.600000000002</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5">
+        <v>77</v>
+      </c>
+      <c r="O18" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P18" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>1</v>
+      </c>
+      <c r="R18" s="3">
+        <v>6</v>
+      </c>
+      <c r="S18" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T18" s="3">
+        <v>400</v>
+      </c>
+      <c r="U18" s="3">
+        <v>370</v>
+      </c>
+      <c r="V18" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="14">
+        <v>30</v>
+      </c>
+      <c r="B19" s="14">
+        <v>22</v>
+      </c>
+      <c r="C19" s="15">
+        <v>4</v>
+      </c>
+      <c r="D19" s="15">
+        <v>1764</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="17">
+        <v>21015</v>
+      </c>
+      <c r="H19" s="18">
+        <f t="shared" si="1"/>
+        <v>27319.5</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5">
+        <v>77</v>
+      </c>
+      <c r="O19" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P19" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>1</v>
+      </c>
+      <c r="R19" s="3">
+        <v>6</v>
+      </c>
+      <c r="S19" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T19" s="3">
+        <v>400</v>
+      </c>
+      <c r="U19" s="3">
+        <v>370</v>
+      </c>
+      <c r="V19" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="14">
+        <v>20</v>
+      </c>
+      <c r="B20" s="14">
+        <v>15</v>
+      </c>
+      <c r="C20" s="15">
+        <v>4</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1752</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="17">
+        <v>24678</v>
+      </c>
+      <c r="H20" s="18">
+        <f t="shared" si="1"/>
+        <v>32081.4</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5">
+        <v>77</v>
+      </c>
+      <c r="O20" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P20" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>1</v>
+      </c>
+      <c r="R20" s="3">
+        <v>6</v>
+      </c>
+      <c r="S20" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T20" s="3">
+        <v>400</v>
+      </c>
+      <c r="U20" s="3">
+        <v>370</v>
+      </c>
+      <c r="V20" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="14">
+        <v>25</v>
+      </c>
+      <c r="B21" s="14">
+        <v>18.5</v>
+      </c>
+      <c r="C21" s="15">
+        <v>4</v>
+      </c>
+      <c r="D21" s="15">
+        <v>1752</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="17">
+        <v>30656</v>
+      </c>
+      <c r="H21" s="18">
+        <f t="shared" si="1"/>
+        <v>39852.800000000003</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="J21" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5">
+        <v>77</v>
+      </c>
+      <c r="O21" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P21" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>1</v>
+      </c>
+      <c r="R21" s="3">
+        <v>6</v>
+      </c>
+      <c r="S21" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T21" s="3">
+        <v>400</v>
+      </c>
+      <c r="U21" s="3">
+        <v>370</v>
+      </c>
+      <c r="V21" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="14">
+        <v>25</v>
+      </c>
+      <c r="B22" s="14">
+        <v>18.5</v>
+      </c>
+      <c r="C22" s="15">
+        <v>6</v>
+      </c>
+      <c r="D22" s="15">
+        <v>1176</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" s="17">
+        <v>34030</v>
+      </c>
+      <c r="H22" s="18">
+        <f t="shared" si="1"/>
+        <v>44239</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5">
+        <v>77</v>
+      </c>
+      <c r="O22" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P22" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>1</v>
+      </c>
+      <c r="R22" s="3">
+        <v>6</v>
+      </c>
+      <c r="S22" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T22" s="3">
+        <v>400</v>
+      </c>
+      <c r="U22" s="3">
+        <v>370</v>
+      </c>
+      <c r="V22" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="14">
+        <v>30</v>
+      </c>
+      <c r="B23" s="14">
+        <v>22</v>
+      </c>
+      <c r="C23" s="15">
+        <v>4</v>
+      </c>
+      <c r="D23" s="15">
+        <v>1764</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="17">
+        <v>10990</v>
+      </c>
+      <c r="H23" s="18">
+        <f>G23*1.3</f>
+        <v>14287</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5">
+        <v>77</v>
+      </c>
+      <c r="O23" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P23" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q23" s="5">
+        <v>1</v>
+      </c>
+      <c r="R23" s="3">
+        <v>6</v>
+      </c>
+      <c r="S23" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T23" s="3">
+        <v>400</v>
+      </c>
+      <c r="U23" s="3">
+        <v>370</v>
+      </c>
+      <c r="V23" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="14">
+        <v>40</v>
+      </c>
+      <c r="B24" s="14">
+        <v>30</v>
+      </c>
+      <c r="C24" s="15">
+        <v>4</v>
+      </c>
+      <c r="D24" s="15">
+        <v>1764</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="17">
+        <v>10990</v>
+      </c>
+      <c r="H24" s="18">
+        <f>G24*1.3</f>
+        <v>14287</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5">
+        <v>77</v>
+      </c>
+      <c r="O24" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P24" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q24" s="5">
+        <v>1</v>
+      </c>
+      <c r="R24" s="3">
+        <v>6</v>
+      </c>
+      <c r="S24" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T24" s="3">
+        <v>400</v>
+      </c>
+      <c r="U24" s="3">
+        <v>370</v>
+      </c>
+      <c r="V24" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="14">
+        <v>50</v>
+      </c>
+      <c r="B25" s="14">
+        <v>37</v>
+      </c>
+      <c r="C25" s="15">
+        <v>4</v>
+      </c>
+      <c r="D25" s="15">
+        <v>1764</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" s="17">
+        <v>15617</v>
+      </c>
+      <c r="H25" s="18">
+        <f t="shared" ref="H25:H29" si="2">G25*1.3</f>
+        <v>20302.100000000002</v>
+      </c>
+      <c r="I25" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="J25" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5">
+        <v>77</v>
+      </c>
+      <c r="O25" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P25" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q25" s="5">
+        <v>1</v>
+      </c>
+      <c r="R25" s="3">
+        <v>6</v>
+      </c>
+      <c r="S25" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T25" s="3">
+        <v>400</v>
+      </c>
+      <c r="U25" s="3">
+        <v>370</v>
+      </c>
+      <c r="V25" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="14">
+        <v>60</v>
+      </c>
+      <c r="B26" s="14">
+        <v>45</v>
+      </c>
+      <c r="C26" s="15">
+        <v>4</v>
+      </c>
+      <c r="D26" s="15">
+        <v>1770</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G26" s="17">
+        <v>21015</v>
+      </c>
+      <c r="H26" s="18">
+        <f t="shared" si="2"/>
+        <v>27319.5</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="J26" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5">
+        <v>77</v>
+      </c>
+      <c r="O26" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P26" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>1</v>
+      </c>
+      <c r="R26" s="3">
+        <v>6</v>
+      </c>
+      <c r="S26" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T26" s="3">
+        <v>400</v>
+      </c>
+      <c r="U26" s="3">
+        <v>370</v>
+      </c>
+      <c r="V26" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="14">
+        <v>75</v>
+      </c>
+      <c r="B27" s="14">
+        <v>55</v>
+      </c>
+      <c r="C27" s="15">
+        <v>4</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1770</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" s="17">
+        <v>24678</v>
+      </c>
+      <c r="H27" s="18">
+        <f t="shared" si="2"/>
+        <v>32081.4</v>
+      </c>
+      <c r="I27" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="J27" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5">
+        <v>77</v>
+      </c>
+      <c r="O27" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P27" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q27" s="5">
+        <v>1</v>
+      </c>
+      <c r="R27" s="3">
+        <v>6</v>
+      </c>
+      <c r="S27" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T27" s="3">
+        <v>400</v>
+      </c>
+      <c r="U27" s="3">
+        <v>370</v>
+      </c>
+      <c r="V27" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="14">
+        <v>100</v>
+      </c>
+      <c r="B28" s="14">
+        <v>75</v>
+      </c>
+      <c r="C28" s="15">
+        <v>4</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1776</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G28" s="17">
+        <v>30656</v>
+      </c>
+      <c r="H28" s="18">
+        <f t="shared" si="2"/>
+        <v>39852.800000000003</v>
+      </c>
+      <c r="I28" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="J28" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5">
+        <v>77</v>
+      </c>
+      <c r="O28" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P28" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>1</v>
+      </c>
+      <c r="R28" s="3">
+        <v>6</v>
+      </c>
+      <c r="S28" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T28" s="3">
+        <v>400</v>
+      </c>
+      <c r="U28" s="3">
+        <v>370</v>
+      </c>
+      <c r="V28" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="14">
+        <v>125</v>
+      </c>
+      <c r="B29" s="14">
+        <v>90</v>
+      </c>
+      <c r="C29" s="15">
+        <v>4</v>
+      </c>
+      <c r="D29" s="15">
+        <v>1776</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G29" s="17">
+        <v>34030</v>
+      </c>
+      <c r="H29" s="18">
+        <f t="shared" si="2"/>
+        <v>44239</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5">
+        <v>77</v>
+      </c>
+      <c r="O29" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P29" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q29" s="5">
+        <v>1</v>
+      </c>
+      <c r="R29" s="3">
+        <v>6</v>
+      </c>
+      <c r="S29" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T29" s="3">
+        <v>400</v>
+      </c>
+      <c r="U29" s="3">
+        <v>370</v>
+      </c>
+      <c r="V29" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="14">
+        <v>150</v>
+      </c>
+      <c r="B30" s="14">
+        <v>110</v>
+      </c>
+      <c r="C30" s="15">
+        <v>4</v>
+      </c>
+      <c r="D30" s="15">
+        <v>1776</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G30" s="17">
+        <v>10990</v>
+      </c>
+      <c r="H30" s="18">
+        <f>G30*1.3</f>
+        <v>14287</v>
+      </c>
+      <c r="I30" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5">
+        <v>77</v>
+      </c>
+      <c r="O30" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P30" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>1</v>
+      </c>
+      <c r="R30" s="3">
+        <v>6</v>
+      </c>
+      <c r="S30" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T30" s="3">
+        <v>400</v>
+      </c>
+      <c r="U30" s="3">
+        <v>370</v>
+      </c>
+      <c r="V30" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="14">
+        <v>180</v>
+      </c>
+      <c r="B31" s="14">
+        <v>132</v>
+      </c>
+      <c r="C31" s="15">
+        <v>4</v>
+      </c>
+      <c r="D31" s="15">
+        <v>1776</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G31" s="17">
+        <v>10990</v>
+      </c>
+      <c r="H31" s="18">
+        <f>G31*1.3</f>
+        <v>14287</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="J31" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5">
+        <v>77</v>
+      </c>
+      <c r="O31" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P31" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q31" s="5">
+        <v>1</v>
+      </c>
+      <c r="R31" s="3">
+        <v>6</v>
+      </c>
+      <c r="S31" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T31" s="3">
+        <v>400</v>
+      </c>
+      <c r="U31" s="3">
+        <v>370</v>
+      </c>
+      <c r="V31" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="14">
+        <v>200</v>
+      </c>
+      <c r="B32" s="14">
+        <v>160</v>
+      </c>
+      <c r="C32" s="15">
+        <v>4</v>
+      </c>
+      <c r="D32" s="15">
+        <v>1776</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" s="17">
+        <v>12822</v>
+      </c>
+      <c r="H32" s="18">
+        <f t="shared" ref="H32:H37" si="3">G32*1.3</f>
+        <v>16668.600000000002</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5">
+        <v>77</v>
+      </c>
+      <c r="O32" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P32" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>1</v>
+      </c>
+      <c r="R32" s="3">
+        <v>6</v>
+      </c>
+      <c r="S32" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T32" s="3">
+        <v>400</v>
+      </c>
+      <c r="U32" s="3">
+        <v>370</v>
+      </c>
+      <c r="V32" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="14">
+        <v>270</v>
+      </c>
+      <c r="B33" s="14">
+        <v>200</v>
+      </c>
+      <c r="C33" s="15">
+        <v>4</v>
+      </c>
+      <c r="D33" s="15">
+        <v>1776</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" s="17">
+        <v>15617</v>
+      </c>
+      <c r="H33" s="18">
+        <f t="shared" si="3"/>
+        <v>20302.100000000002</v>
+      </c>
+      <c r="I33" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="J33" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5">
+        <v>77</v>
+      </c>
+      <c r="O33" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P33" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q33" s="5">
+        <v>1</v>
+      </c>
+      <c r="R33" s="3">
+        <v>6</v>
+      </c>
+      <c r="S33" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T33" s="3">
+        <v>400</v>
+      </c>
+      <c r="U33" s="3">
+        <v>370</v>
+      </c>
+      <c r="V33" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="14">
+        <v>340</v>
+      </c>
+      <c r="B34" s="14">
+        <v>250</v>
+      </c>
+      <c r="C34" s="15">
+        <v>4</v>
+      </c>
+      <c r="D34" s="15">
+        <v>1788</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34" s="17">
+        <v>19472</v>
+      </c>
+      <c r="H34" s="18">
+        <f t="shared" si="3"/>
+        <v>25313.600000000002</v>
+      </c>
+      <c r="I34" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="J34" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5">
+        <v>77</v>
+      </c>
+      <c r="O34" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P34" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>1</v>
+      </c>
+      <c r="R34" s="3">
+        <v>6</v>
+      </c>
+      <c r="S34" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T34" s="3">
+        <v>400</v>
+      </c>
+      <c r="U34" s="3">
+        <v>370</v>
+      </c>
+      <c r="V34" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="14">
+        <v>430</v>
+      </c>
+      <c r="B35" s="14">
+        <v>315</v>
+      </c>
+      <c r="C35" s="15">
+        <v>4</v>
+      </c>
+      <c r="D35" s="15">
+        <v>1788</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" s="17">
+        <v>21015</v>
+      </c>
+      <c r="H35" s="18">
+        <f t="shared" si="3"/>
+        <v>27319.5</v>
+      </c>
+      <c r="I35" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5">
+        <v>77</v>
+      </c>
+      <c r="O35" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P35" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q35" s="5">
+        <v>1</v>
+      </c>
+      <c r="R35" s="3">
+        <v>6</v>
+      </c>
+      <c r="S35" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T35" s="3">
+        <v>400</v>
+      </c>
+      <c r="U35" s="3">
+        <v>370</v>
+      </c>
+      <c r="V35" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="14">
+        <v>475</v>
+      </c>
+      <c r="B36" s="14">
+        <v>355</v>
+      </c>
+      <c r="C36" s="15">
+        <v>4</v>
+      </c>
+      <c r="D36" s="15">
+        <v>1788</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G36" s="17">
+        <v>24678</v>
+      </c>
+      <c r="H36" s="18">
+        <f t="shared" si="3"/>
+        <v>32081.4</v>
+      </c>
+      <c r="I36" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="J36" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5">
+        <v>77</v>
+      </c>
+      <c r="O36" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P36" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>1</v>
+      </c>
+      <c r="R36" s="3">
+        <v>6</v>
+      </c>
+      <c r="S36" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T36" s="3">
+        <v>400</v>
+      </c>
+      <c r="U36" s="3">
+        <v>370</v>
+      </c>
+      <c r="V36" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="99.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="14">
+        <v>535</v>
+      </c>
+      <c r="B37" s="14">
+        <v>400</v>
+      </c>
+      <c r="C37" s="15">
+        <v>4</v>
+      </c>
+      <c r="D37" s="15">
+        <v>1788</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G37" s="17">
+        <v>30656</v>
+      </c>
+      <c r="H37" s="18">
+        <f t="shared" si="3"/>
+        <v>39852.800000000003</v>
+      </c>
+      <c r="I37" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="J37" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5">
+        <v>77</v>
+      </c>
+      <c r="O37" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="P37" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="Q37" s="5">
+        <v>1</v>
+      </c>
+      <c r="R37" s="3">
+        <v>6</v>
+      </c>
+      <c r="S37" s="6">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T37" s="3">
+        <v>400</v>
+      </c>
+      <c r="U37" s="3">
+        <v>370</v>
+      </c>
+      <c r="V37" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="S4:U4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{255A5258-1096-4E31-83BB-3E76165F918F}">
+  <dimension ref="A1:A31"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A1" s="20" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A2" s="19" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A3" s="19" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A4" s="20" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A5" s="20" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A6" s="19" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A7" s="19" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A8" s="19" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A9" s="20" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A10" s="19" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A11" s="19" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A12" s="20" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A13" s="20" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A14" s="19" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A15" s="19" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A16" s="19" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A17" s="20" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A18" s="20" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A19" s="19" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A20" s="20" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A21" s="19" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A22" s="19" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A23" s="19" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A24" s="20" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A25" s="20" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A26" s="19" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A27" s="19" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A28" s="20" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A29" s="20" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A30" s="19" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="276.75" x14ac:dyDescent="0.45">
+      <c r="A31" s="19" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>